--- a/docs/xlsx/jobs-2026-10-02.xlsx
+++ b/docs/xlsx/jobs-2026-10-02.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="731">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,2182 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>2026 - AmeriCorps Member Positions Across Montana</t>
+  </si>
+  <si>
+    <t>Montana Fish, Wildlife &amp; Parks AmeriCorps</t>
+  </si>
+  <si>
+    <t>Helena, MT</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$512 per week</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-2026---americorps-member-positions-across-montana-helena-montana/5528025217</t>
+  </si>
+  <si>
+    <t>2027 Forestry Summer Internship - Spokane, WA</t>
+  </si>
+  <si>
+    <t>American Forest Management, Inc.</t>
+  </si>
+  <si>
+    <t>Spokane, WA</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$21 - $24 per hour</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-2027-forestry-summer-internship---spokane-wa-spokane-washington/4731569866</t>
+  </si>
+  <si>
+    <t>AmeriCorps Riparian Restoration Strike Team Assistant Crew Leader</t>
+  </si>
+  <si>
+    <t>Western Colorado Conservation Corps</t>
+  </si>
+  <si>
+    <t>Grand Junction, CO</t>
+  </si>
+  <si>
+    <t>$645 per week</t>
+  </si>
+  <si>
+    <t>general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-americorps-riparian-restoration-strike-team-assistant-crew-leader-grand-junction-colorado/6473314485</t>
+  </si>
+  <si>
+    <t>AmeriCorps Riparian Restoration Strike Team Crew Leader</t>
+  </si>
+  <si>
+    <t>$664 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-americorps-riparian-restoration-strike-team-crew-leader-grand-junction-colorado/2239226465</t>
+  </si>
+  <si>
+    <t>AmeriCorps Riparian Restoration Strike Team Crew Member</t>
+  </si>
+  <si>
+    <t>$600 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-americorps-riparian-restoration-strike-team-crew-member-grand-junction-colorado/5645928789</t>
+  </si>
+  <si>
+    <t>ARD Helene Recovery Trail Assistant Crew Leader</t>
+  </si>
+  <si>
+    <t>Conservation Corps North Carolina</t>
+  </si>
+  <si>
+    <t>Bahama, NC</t>
+  </si>
+  <si>
+    <t>$650 per week</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ard-helene-recovery-trail-assistant-crew-leader-bahama-north-carolina/1997642581</t>
+  </si>
+  <si>
+    <t>ARD Helene Recovery Trail Crew Leader</t>
+  </si>
+  <si>
+    <t>Old Fort, NC</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$925 - $1,125 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ard-helene-recovery-trail-crew-leader-old-fort-north-carolina/9189801220</t>
+  </si>
+  <si>
+    <t>Calumet Conservation Corps Crew Member</t>
+  </si>
+  <si>
+    <t>Friends of the Forest Preserves</t>
+  </si>
+  <si>
+    <t>South Holland, IL</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$18 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-calumet-conservation-corps-crew-member-south-holland-illinois/7915515887</t>
+  </si>
+  <si>
+    <t>Chief Executive Officer</t>
+  </si>
+  <si>
+    <t>Nature &amp; Culture International</t>
+  </si>
+  <si>
+    <t>Remote, CA</t>
+  </si>
+  <si>
+    <t>$275,000 - $325,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-chief-executive-officer-remote-california/8999591004</t>
+  </si>
+  <si>
+    <t>Community Specialist</t>
+  </si>
+  <si>
+    <t>EarthCorps</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>$3,600 per month</t>
+  </si>
+  <si>
+    <t>environmental-education-general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-community-specialist-seattle-washington/5126685856</t>
+  </si>
+  <si>
+    <t>Conservation Corps Assistant Crew Leader</t>
+  </si>
+  <si>
+    <t>environmental-education-general-stewardship-outdoor-recreation-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-corps-crew-member-grand-junction-colorado/1226305780</t>
+  </si>
+  <si>
+    <t>Conservation Corps Crew Leader</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-corps-crew-member-grand-junction-colorado/4770864952</t>
+  </si>
+  <si>
+    <t>Conservation Corps Crew Member</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-corps-crew-member-grand-junction-colorado/6377677641</t>
+  </si>
+  <si>
+    <t>Crewleader</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-crewleader-seattle-washington/5124424131</t>
+  </si>
+  <si>
+    <t>Crewmember</t>
+  </si>
+  <si>
+    <t>$3,300 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-crewmember-seattle-washington/7842695974</t>
+  </si>
+  <si>
+    <t>Director of Programs &amp; Operations</t>
+  </si>
+  <si>
+    <t>ecoLatinos</t>
+  </si>
+  <si>
+    <t>College Park, MD</t>
+  </si>
+  <si>
+    <t>$65,000 - $78,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-programs--operations-college-park-maryland/5626100707</t>
+  </si>
+  <si>
+    <t>District Administrator</t>
+  </si>
+  <si>
+    <t>Hill County Conservation District</t>
+  </si>
+  <si>
+    <t>Havre, MT</t>
+  </si>
+  <si>
+    <t>$24 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-district-administrator-havre-montana/4780067355</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Southeastern Wisconsin Invasive Species Consortium, Inc</t>
+  </si>
+  <si>
+    <t>Milwaukee, WI</t>
+  </si>
+  <si>
+    <t>$36,400 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-milwaukee-wisconsin/5561086841</t>
+  </si>
+  <si>
+    <t>Executive Vice President</t>
+  </si>
+  <si>
+    <t>Pacific Forest Trust</t>
+  </si>
+  <si>
+    <t>San Francisco, CA</t>
+  </si>
+  <si>
+    <t>$160,000 - $190,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-forestry-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-vice-president-san-francisco-california/9809165614</t>
+  </si>
+  <si>
+    <t>Fisheries Wildlife Biologist II</t>
+  </si>
+  <si>
+    <t>Kansas Department of Wildlife and Parks</t>
+  </si>
+  <si>
+    <t>Glen Elder, KS</t>
+  </si>
+  <si>
+    <t>$28.30 per hour</t>
+  </si>
+  <si>
+    <t>fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fisheries-wildlife-biologist-ii-glen-elder-kansas/3334222506</t>
+  </si>
+  <si>
+    <t>GRD Helene Recovery Trail Crew Leader</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-grd-helene-recovery-trail-crew-leader-old-fort-north-carolina/1895985328</t>
+  </si>
+  <si>
+    <t>HAWKs Educator</t>
+  </si>
+  <si>
+    <t>HAWKs Crescenta Valley</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>$25 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-hawks-educator-los-angeles-california/3170724915</t>
+  </si>
+  <si>
+    <t>Helene Recovery Vegetation Management Crew Member</t>
+  </si>
+  <si>
+    <t>forestry-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-helene-recovery-vegetation-management-crew-member-old-fort-north-carolina/5022806715</t>
+  </si>
+  <si>
+    <t>Hubbard Conservation Fellow</t>
+  </si>
+  <si>
+    <t>The Nature Conservancy</t>
+  </si>
+  <si>
+    <t>Wood River, NE</t>
+  </si>
+  <si>
+    <t>$17.85 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-restoration-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-hubbard-conservation-fellow-wood-river-kansas/5307789502</t>
+  </si>
+  <si>
+    <t>Illinois Agricultural and Conservation Technical Specialist</t>
+  </si>
+  <si>
+    <t>American Farmland Trust</t>
+  </si>
+  <si>
+    <t>Effingham, IL</t>
+  </si>
+  <si>
+    <t>$70,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology-land-trust-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-illinois-agricultural-and-conservation-technical-specialist-effingham-illinois/2950498963</t>
+  </si>
+  <si>
+    <t>Lecturer in Systems Thinking for the Future of Agriculture</t>
+  </si>
+  <si>
+    <t>The School for Field Studies</t>
+  </si>
+  <si>
+    <t>Greve, Europe</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>$38,000 - $42,000 per year</t>
+  </si>
+  <si>
+    <t>policy-and-law-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-lecturer-in-systems-thinking-for-the-future-of-agriculture-greve-europe/1013523521</t>
+  </si>
+  <si>
+    <t>Lecturer in Tropical Marine Ecology</t>
+  </si>
+  <si>
+    <t>South Caicos, Other</t>
+  </si>
+  <si>
+    <t>$40,000 - $43,000 per year</t>
+  </si>
+  <si>
+    <t>marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-lecturer-in-tropical-marine-ecology-south-caicos-other/5201074496</t>
+  </si>
+  <si>
+    <t>Maintenance Aide III - Park Stewardship</t>
+  </si>
+  <si>
+    <t>City of Bellingham</t>
+  </si>
+  <si>
+    <t>Bellingham, WA</t>
+  </si>
+  <si>
+    <t>$23.68 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-maintenance-aide-iii---park-stewardship-bellingham-washington/8278258034</t>
+  </si>
+  <si>
+    <t>Maintenance Technicians (NPS, Haleakala National Park (Kipahulu))</t>
+  </si>
+  <si>
+    <t>Great Basin Institute</t>
+  </si>
+  <si>
+    <t>Makawao, HI</t>
+  </si>
+  <si>
+    <t>$26.30/hr</t>
+  </si>
+  <si>
+    <t>outdoor-recreation-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-maintenance-technicians-nps-haleakala-national-park-kipahulu-makawao-hawaii/1130208372</t>
+  </si>
+  <si>
+    <t>Managing Director of Development</t>
+  </si>
+  <si>
+    <t>Pheasants Forever, Inc., and Quail Forever</t>
+  </si>
+  <si>
+    <t>Midwest preferred, Other</t>
+  </si>
+  <si>
+    <t>$100,000 - $120,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-managing-director-of-development-midwest-msp-metro-area-preferred-minnesota/5796280824</t>
+  </si>
+  <si>
+    <t>Marine Biologist (ASM)- Gloucester, MA</t>
+  </si>
+  <si>
+    <t>A.I.S. Inc.</t>
+  </si>
+  <si>
+    <t>Gloucester, MA</t>
+  </si>
+  <si>
+    <t>$19 - $23.57 per hour</t>
+  </si>
+  <si>
+    <t>fisheries-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-marine-biologist-asm--gloucester-ma-gloucester-massachusetts/3320338952</t>
+  </si>
+  <si>
+    <t>Marine Biologist- Alaska</t>
+  </si>
+  <si>
+    <t>Anchorage, AK</t>
+  </si>
+  <si>
+    <t>$5,100 - $8,100 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-marine-biologist--alaska-anchorage-alaska/2702249726</t>
+  </si>
+  <si>
+    <t>Marine Biology Instructor and Trip Leader - Summer 2027</t>
+  </si>
+  <si>
+    <t>Broadreach Adventures, LLC</t>
+  </si>
+  <si>
+    <t>Raleigh, NC</t>
+  </si>
+  <si>
+    <t>$2,000 - $3,000 per year</t>
+  </si>
+  <si>
+    <t>environmental-education-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-marine-biology-instructor-and--trip-leader---summer-2027-raleigh-north-carolina/2675861953</t>
+  </si>
+  <si>
+    <t>Muleshoe Preserve Steward</t>
+  </si>
+  <si>
+    <t>Willcox, AZ</t>
+  </si>
+  <si>
+    <t>$21.10 - $22.42 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-land-trust-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-muleshoe-preserve-steward-willcox-arizona/1194553831</t>
+  </si>
+  <si>
+    <t>NPS Historic Preservation Training Center – Traditional Trades Advancement Program and Youth Empowerment Stewards – Olympic National Park – AmeriCorps</t>
+  </si>
+  <si>
+    <t>Conservation Legacy</t>
+  </si>
+  <si>
+    <t>Port Angeles, WA</t>
+  </si>
+  <si>
+    <t>$720 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-nps-historic-preservation-training-center--traditional-trades-advancement-program-and-youth-empowerment-stewardsolympic-national-park-americorps-port-angeles-washington/6536716965</t>
+  </si>
+  <si>
+    <t>NWTF Storyteller - Northeast</t>
+  </si>
+  <si>
+    <t>National Wild Turkey Federation</t>
+  </si>
+  <si>
+    <t>Buffalo, NY</t>
+  </si>
+  <si>
+    <t>$51,901 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-nwtf-storyteller---northeast-buffalo-new-york/5558099113</t>
+  </si>
+  <si>
+    <t>OPS Biological Scientist IV</t>
+  </si>
+  <si>
+    <t>Florida Fish and Wildlife Conservation Commission; Division of Marine Fisheries Management</t>
+  </si>
+  <si>
+    <t>Tallahassee, FL</t>
+  </si>
+  <si>
+    <t>$24.32 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ops-biological-scientist-iv-tallahassee-florida/9433244411</t>
+  </si>
+  <si>
+    <t>Jacksonville, FL</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ops-biological-scientist-iv-jacksonville-florida/9940363437</t>
+  </si>
+  <si>
+    <t>Florida Fish and Wildlife Conservation Commission</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ops-biological-scientist-iv-jacksonville-florida/7865404492</t>
+  </si>
+  <si>
+    <t>Palos Conservation Corps Crew Manager</t>
+  </si>
+  <si>
+    <t>Willow Springs, IL</t>
+  </si>
+  <si>
+    <t>$28.34 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-palos-conservation-corps-crew-manager-willow-springs-illinois/9665070353</t>
+  </si>
+  <si>
+    <t>Pikes Peak Sentinel Landscape Coordinator</t>
+  </si>
+  <si>
+    <t>LegacyWorks Group</t>
+  </si>
+  <si>
+    <t>Remote, CO</t>
+  </si>
+  <si>
+    <t>$85,000 - $130,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-pikes-peak-sentinel-landscape-coordinator-remote-colorado/4016522215</t>
+  </si>
+  <si>
+    <t>Public Interest Environmental Law Fellow</t>
+  </si>
+  <si>
+    <t>Environmental Law Institute</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>$69,000 per year</t>
+  </si>
+  <si>
+    <t>policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-public-interest-environmental-law-fellow-washington-dc/1663721751</t>
+  </si>
+  <si>
+    <t>Recreation Instructor</t>
+  </si>
+  <si>
+    <t>$25.10 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-recreation-instructor-bellingham-washington/1778119777</t>
+  </si>
+  <si>
+    <t>Resilient Cities Program Manager</t>
+  </si>
+  <si>
+    <t>Spatial Informatics Group Natural Assets Laboratory</t>
+  </si>
+  <si>
+    <t>Albuquerque, NM</t>
+  </si>
+  <si>
+    <t>$72,000 - $93,600 per year</t>
+  </si>
+  <si>
+    <t>hydrology-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-resilient-cities-program-manager-albuquerque-new-mexico/7834513969</t>
+  </si>
+  <si>
+    <t>Resource Assessment Program Supervisor</t>
+  </si>
+  <si>
+    <t>Minnesota Department of Natural Resources, Division of Forestry</t>
+  </si>
+  <si>
+    <t>Grand Rapids, MN</t>
+  </si>
+  <si>
+    <t>$40.23 - $57.94 / hourly; $84,000 - $120,978 / annually</t>
+  </si>
+  <si>
+    <t>admin-leadership-forestry-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-resource-assessment-program-supervisor-grand-rapids-minnesota/4900750661</t>
+  </si>
+  <si>
+    <t>Salt Watch Coordinator</t>
+  </si>
+  <si>
+    <t>Izaak Walton League of America</t>
+  </si>
+  <si>
+    <t>Gaithersburg, MD</t>
+  </si>
+  <si>
+    <t>$46,000 - $50,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-salt-watch-coordinator-gaithersburg-maryland/4326097230</t>
+  </si>
+  <si>
+    <t>Scientific Research Specialist - Wild Blueberries</t>
+  </si>
+  <si>
+    <t>University of Maine</t>
+  </si>
+  <si>
+    <t>Orono, ME</t>
+  </si>
+  <si>
+    <t>$21.93 per hour</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-scientific-research-specialist---wild-blueberries-orono-maine/5515381807</t>
+  </si>
+  <si>
+    <t>Seasonal Education Coordinator (Georgia)</t>
+  </si>
+  <si>
+    <t>Appalachian Trail Conservancy</t>
+  </si>
+  <si>
+    <t>US, Other</t>
+  </si>
+  <si>
+    <t>$19 - $21 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-seasonal-education-coordinator-georgia-us-other/3956559771</t>
+  </si>
+  <si>
+    <t>Seasonal Ridgerunner (Great Smoky Mountains)</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-seasonal-ridgerunner-great-smoky-mountains-us-other/4909210064</t>
+  </si>
+  <si>
+    <t>Seasonal Ridgerunner (North Georgia)</t>
+  </si>
+  <si>
+    <t>US, Remote</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-seasonal-ridgerunner-north-georgia-us-remote/2574791181</t>
+  </si>
+  <si>
+    <t>Seasonal Trail Crew Member (Great Smoky Mountains)</t>
+  </si>
+  <si>
+    <t>Crew base near Gatlinburg, TN. Work in GA, NC, and TN., TN</t>
+  </si>
+  <si>
+    <t>$21 - $22 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-seasonal-trail-crew-member-great-smoky-mountains-us-other/6786672000</t>
+  </si>
+  <si>
+    <t>Senior Manager, Corporate Partnerships &amp; Communications</t>
+  </si>
+  <si>
+    <t>Bonneville Environmental Foundation (BEF)</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>$80,000 - $92,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-manager-corporate-partnerships--communications-portland-oregon/9489108077</t>
+  </si>
+  <si>
+    <t>State Parks Mountains Trail Assistant Crew Leader</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-state-parks-mountains-trail-assistant-crew-leader-old-fort-north-carolina/7724506945</t>
+  </si>
+  <si>
+    <t>State Parks Piedmont Trail Crew Leader</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-state-parks-piedmont-trail-crew-leader-bahama-north-carolina/8605949414</t>
+  </si>
+  <si>
+    <t>Trail Program Manager</t>
+  </si>
+  <si>
+    <t>Buena Vista Singletrack Coalition</t>
+  </si>
+  <si>
+    <t>Buena Vista, CO</t>
+  </si>
+  <si>
+    <t>$65,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-trail-program-manager-buena-vista-colorado/6114530548</t>
+  </si>
+  <si>
+    <t>WaterShed Visitor Services Specialist</t>
+  </si>
+  <si>
+    <t>City of Boise</t>
+  </si>
+  <si>
+    <t>Boise, ID</t>
+  </si>
+  <si>
+    <t>$17 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-watershed-visitor-services-specialist-boise-idaho/5167960357</t>
+  </si>
+  <si>
+    <t>Western Snowy Plover Conservation Technician</t>
+  </si>
+  <si>
+    <t>Point Blue Conservation Science</t>
+  </si>
+  <si>
+    <t>Monterey, CA</t>
+  </si>
+  <si>
+    <t>$23.15 per hour</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-western-snowy-plover-conservation-technician-monterey-california/1886315675</t>
+  </si>
+  <si>
+    <t>🌍 Líder de Equipo F2F | Donantes Individuales | Turno Mañana o Tarde | CABA</t>
+  </si>
+  <si>
+    <t>Ingeniería Sin Fronteras Argentina</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d4df8ed6a7a3475487538a2f00e413e9-lider-de-equipo-f2f-donantes-individuales-turno-manana-o-tarde-caba-ingenieria-sin-fronteras-argentina-buenos-aires</t>
+  </si>
+  <si>
+    <t>Academic Tutor</t>
+  </si>
+  <si>
+    <t>Japanese Community Youth Council</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 23.50 - 23.50/hour</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9e0327eceba9441fa0a103a7b82f86a3-academic-tutor-japanese-community-youth-council-san-francisco</t>
+  </si>
+  <si>
+    <t>Access to Justice Fellows Program Manager</t>
+  </si>
+  <si>
+    <t>Lawyers Clearinghouse on Affordable Housing and Homelessness</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 42000.00 - 48000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/601fda401e824739b7f226ba0f43481a-access-to-justice-fellows-program-manager-lawyers-clearinghouse-on-affordable-housing-and-homelessness-boston</t>
+  </si>
+  <si>
+    <t>Adjunct Teacher</t>
+  </si>
+  <si>
+    <t>exalt youth</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 18000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d3ebb3e3f1a40d39c4fecce0b3bfe1e-adjunct-teacher-exalt-youth-new-york</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVE ASSISTANT - Washington State / State of Louisiana</t>
+  </si>
+  <si>
+    <t>In The Works, LLC</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, Philanthropy, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/2fb793d0fa5b41d6a43e34ca60fb6781-administrative-assistant-washington-state-state-of-louisiana-in-the-works-llc-seattle</t>
+  </si>
+  <si>
+    <t>Advocacy and Policy Manager</t>
+  </si>
+  <si>
+    <t>Asian American Federation</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 91000.00 - 97000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Human Rights Civil Liberties, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f69f2920c3141469859909d0dbff854-advocacy-and-policy-manager-asian-american-federation-new-york</t>
+  </si>
+  <si>
+    <t>Affiliate Development Consultant – NAMI Capitol Area</t>
+  </si>
+  <si>
+    <t>NAMI Illinois</t>
+  </si>
+  <si>
+    <t>Remote (Illinois)</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Communications Access, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b97ae037479045b8b7646eda5553af43-affiliate-development-consultant-nami-capitol-area-nami-illinois-springfield</t>
+  </si>
+  <si>
+    <t>Affiliate Development Consultant – NAMI Jackson County</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d995e7fabec446c2bf74df0d9e7e6885-affiliate-development-consultant-nami-jackson-county-nami-illinois-chicago</t>
+  </si>
+  <si>
+    <t>Affiliate Development Consultant – NAMI Kankakee County</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/794bce32f81a4519b6595db1b2bb9f18-affiliate-development-consultant-nami-kankakee-county-nami-illinois-kankakee</t>
+  </si>
+  <si>
+    <t>Asociadx en Finanzas para la Transición Energética Justa,</t>
+  </si>
+  <si>
+    <t>GFLAC</t>
+  </si>
+  <si>
+    <t>Remote (MX)</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d0dfbcb711014aa488d1d30c95113101-asociadx-en-finanzas-para-la-transicion-energetica-justa-gflac-tlalnepantla-de-baz</t>
+  </si>
+  <si>
+    <t>Associate Director, Research, Data &amp; Learning</t>
+  </si>
+  <si>
+    <t>Sakhi for South Asian Survivors</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Human Rights Civil Liberties, Sexual Abuse Human Trafficking</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cfab4a77355b49708b74f297e99efb5c-associate-director-research-data-learning-sakhi-for-south-asian-survivors-new-york</t>
+  </si>
+  <si>
+    <t>Associate, Foundation Relations</t>
+  </si>
+  <si>
+    <t>Civic Nation</t>
+  </si>
+  <si>
+    <t>Remote (Washington, District of Columbia)</t>
+  </si>
+  <si>
+    <t>USD 62600.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/02c2e6fc17be4c2db5e61319f74aad4f-associate-foundation-relations-civic-nation-washington</t>
+  </si>
+  <si>
+    <t>Attorney in Charge</t>
+  </si>
+  <si>
+    <t>Legal Services of the Hudson Valley</t>
+  </si>
+  <si>
+    <t>White Plains, New York</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a0fd2b90747d4c979c01829b62312083-attorney-in-charge-legal-services-of-the-hudson-valley-white-plains</t>
+  </si>
+  <si>
+    <t>Bi-Lingual Case Manager</t>
+  </si>
+  <si>
+    <t>Coalition for the Homeless</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f2dc0bbfea5a43a59e8feffd4ea716bc-bi-lingual-case-manager-coalition-for-the-homeless-new-york</t>
+  </si>
+  <si>
+    <t>Bilingual Housing Counselor I</t>
+  </si>
+  <si>
+    <t>NeighborWorks Affiliates</t>
+  </si>
+  <si>
+    <t>Green Bay, Wisconsin</t>
+  </si>
+  <si>
+    <t>USD 47000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Financial Literacy Personal Finance, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c09704b20cb484da068799775c32e73-bilingual-housing-counselor-i-neighborworks-affiliates-green-bay</t>
+  </si>
+  <si>
+    <t>Branding and Website Specialist</t>
+  </si>
+  <si>
+    <t>BERTHA PROJECT 2</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Education, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/adac7fd7184e43308ad80350dbf90a1f-branding-and-website-specialist-bertha-project-2-wilmette</t>
+  </si>
+  <si>
+    <t>Bronx Community Organizer</t>
+  </si>
+  <si>
+    <t>Office Of the Community Liaison</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/5178d6d2fd1f44d99460c36acfaeca63-bronx-community-organizer-office-of-the-community-liaison-kings-county</t>
+  </si>
+  <si>
+    <t>Business &amp; Finance Manager</t>
+  </si>
+  <si>
+    <t>Puppet Showplace Theater</t>
+  </si>
+  <si>
+    <t>Brookline, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a27f9b3b3d24ded8e0a08f072169eb5-business-finance-manager-puppet-showplace-theater-brookline</t>
+  </si>
+  <si>
+    <t>Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>The Foster Art and Wilderness Foundation (The Foster)</t>
+  </si>
+  <si>
+    <t>Palo Alto, California</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ead9e43953d7479b88a051ad8d402baf-chief-operating-officer-the-foster-art-and-wilderness-foundation-the-foster-palo-alto</t>
+  </si>
+  <si>
+    <t>Chief People Officer, RFK Community Alliance</t>
+  </si>
+  <si>
+    <t>Eos Transition Partners</t>
+  </si>
+  <si>
+    <t>Lancaster, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 175000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/cb9ca5e5b7dc4089a4692f67f9d587d6-chief-people-officer-rfk-community-alliance-eos-transition-partners-lancaster</t>
+  </si>
+  <si>
+    <t>Client Success Manager (Salesforce)</t>
+  </si>
+  <si>
+    <t>Craftsman Technology Group</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/12f6b22399c34b118722c09c0e326034-client-success-manager-salesforce-craftsman-technology-group-boston</t>
+  </si>
+  <si>
+    <t>Communications Associate (Part-Time)</t>
+  </si>
+  <si>
+    <t>Rhode Island Food Policy Council</t>
+  </si>
+  <si>
+    <t>Providence, RI</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 27000.00 - 27000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/24c4a544a5cf4a569d330254b6445ff0-communications-associate-part-time-rhode-island-food-policy-council-providence</t>
+  </si>
+  <si>
+    <t>Communications Manager</t>
+  </si>
+  <si>
+    <t>Elkhorn Slough Foundation</t>
+  </si>
+  <si>
+    <t>Watsonville, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/545546f9bc474c08bc737461786aeec4-communications-manager-elkhorn-slough-foundation-watsonville</t>
+  </si>
+  <si>
+    <t>The GO Project</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a7e65beb53c4490f8e68602fe801f52e-communications-manager-the-go-project-new-york</t>
+  </si>
+  <si>
+    <t>Community Advocate, Housing Rights Program</t>
+  </si>
+  <si>
+    <t>Asian Law Caucus</t>
+  </si>
+  <si>
+    <t>USD 72100.00 - 94074.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2146f56cbc2e4edf907e03d8a73d8861-community-advocate-housing-rights-program-asian-law-caucus-san-francisco</t>
+  </si>
+  <si>
+    <t>CONSUMER STAFF ATTORNEY – BROCKTON LAW OFFICE</t>
+  </si>
+  <si>
+    <t>South Coastal Counties Legal Services Inc.</t>
+  </si>
+  <si>
+    <t>Brockton, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 86500.00 - 113000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1a2a1b6775b343c29f24855d0966aed2-consumer-staff-attorney-brockton-law-office-south-coastal-counties-legal-services-inc-brockton</t>
+  </si>
+  <si>
+    <t>Coordinator, Programs</t>
+  </si>
+  <si>
+    <t>LINK Unlimited Scholars</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 48000.00 - 53000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8c41acbc9c74f3c82fb049e83294ef3-coordinator-programs-link-unlimited-scholars-chicago</t>
+  </si>
+  <si>
+    <t>Corporate Partnerships Associate</t>
+  </si>
+  <si>
+    <t>Rescuing Leftover Cuisine</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/251c21e682f24734945c67e0cc0d3b4e-corporate-partnerships-associate-rescuing-leftover-cuisine-new-york</t>
+  </si>
+  <si>
+    <t>CRM Coordinator &amp; Systems Support</t>
+  </si>
+  <si>
+    <t>Morristown, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/232b0bdb3a3d483bb8cbf8c4e00b244b-crm-coordinator-systems-support-morristown</t>
+  </si>
+  <si>
+    <t>Deputy Information Technology Director</t>
+  </si>
+  <si>
+    <t>Carnegie Endowment for International Peace</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, International Relations, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7a4f28430710461bb227c80d3a6fb87b-deputy-information-technology-director-carnegie-endowment-for-international-peace-washington</t>
+  </si>
+  <si>
+    <t>Development Associate</t>
+  </si>
+  <si>
+    <t>One On One</t>
+  </si>
+  <si>
+    <t>Economic Development, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a21471e9b2374f76b6ea56ea4851bae9-development-associate-one-on-one-chicago</t>
+  </si>
+  <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>Children's Learning Centers of Fairfield County</t>
+  </si>
+  <si>
+    <t>Stamford, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/82eb4fe88c4c4200bda850f2cc5376e5-development-coordinator-childrens-learning-centers-of-fairfield-county-stamford</t>
+  </si>
+  <si>
+    <t>Director of Communications</t>
+  </si>
+  <si>
+    <t>Citizen University</t>
+  </si>
+  <si>
+    <t>USD 102000.00 - 119000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a0a492f42ffd4365adb3305a0d5b6789-director-of-communications-citizen-university-seattle</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Brooklyn Boatworks</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d2a3bbf769bc416ea6b47545cbfc31b8-director-of-development-brooklyn-boatworks-new-york</t>
+  </si>
+  <si>
+    <t>Director of Finance and Administration</t>
+  </si>
+  <si>
+    <t>Sadie Nash Leadership Project</t>
+  </si>
+  <si>
+    <t>Newark, New Jersey</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8fdb1779724b4c22b7cd350b6862bae7-director-of-finance-and-administration-sadie-nash-leadership-project-newark</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8dcd495d865149ef9ff163e450cc0f58-director-of-finance-and-administration-sadie-nash-leadership-project-new-york</t>
+  </si>
+  <si>
+    <t>Director of Operations</t>
+  </si>
+  <si>
+    <t>Filling in The Blanks</t>
+  </si>
+  <si>
+    <t>Norwalk, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1dad9c7be9364bb682d41b6b949c3762-director-of-operations-filling-in-the-blanks-norwalk</t>
+  </si>
+  <si>
+    <t>Philanthropy In Action</t>
+  </si>
+  <si>
+    <t>Tyler, Texas</t>
+  </si>
+  <si>
+    <t>USD 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a7dc48fc35a846a48332d37aa156bf84-director-of-operations-philanthropy-in-action-tyler</t>
+  </si>
+  <si>
+    <t>Education Debt Consumer Assistance Program Advisor</t>
+  </si>
+  <si>
+    <t>Yonkers, New York</t>
+  </si>
+  <si>
+    <t>USD 67235.00 - 84604.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/36d8bae8246a406390bd59df83c98892-education-debt-consumer-assistance-program-advisor-legal-services-of-the-hudson-valley-yonkers</t>
+  </si>
+  <si>
+    <t>Educational Content Design Consultant</t>
+  </si>
+  <si>
+    <t>Coffee Quality Institute</t>
+  </si>
+  <si>
+    <t>Agriculture, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/89b9a08e8f364bfabee0f71fd1c39cf5-educational-content-design-consultant-coffee-quality-institute-aliso-viejo</t>
+  </si>
+  <si>
+    <t>Educational Director - Family Child Care</t>
+  </si>
+  <si>
+    <t>University Settlement Society of New York</t>
+  </si>
+  <si>
+    <t>USD 74500.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/89f17c7f1c9e44498e7367579ab63452-educational-director-family-child-care-university-settlement-society-of-new-york-kings-county</t>
+  </si>
+  <si>
+    <t>Employment Consultant</t>
+  </si>
+  <si>
+    <t>Supported Solution</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Disability, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/defe6b21dbca42669e85e0f730dee114-employment-consultant-supported-solution-seattle</t>
+  </si>
+  <si>
+    <t>Environmental Campaigner</t>
+  </si>
+  <si>
+    <t>Green Corps</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 44450.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ffe4d6a033fd4491a008f33565ac2aa6-environmental-campaigner-green-corps-madison</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef1f135b5c554dfab6141356e9b676f3-environmental-campaigner-green-corps-los-angeles</t>
+  </si>
+  <si>
+    <t>Phoenix, Arizona</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e4cc8b45644a425e863d9821810a7746-environmental-campaigner-green-corps-phoenix</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ddbc738e4cd64fa788bee6491781884a-environmental-campaigner-green-corps-seattle</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9b6a3e08125548c39b5de6445e861a13-environmental-campaigner-green-corps-chicago</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5fef3a382f06458fb5ed8a0ce3787f58-environmental-campaigner-green-corps-minneapolis</t>
+  </si>
+  <si>
+    <t>Charlotte, North Carolina</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5e25cf61b41843ab96be38e3c184983a-environmental-campaigner-green-corps-charlotte</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/579ff6807acd440aae540a6496c1783b-environmental-campaigner-green-corps-boston</t>
+  </si>
+  <si>
+    <t>Atlanta, Georgia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/41e8e507d2d44d31bc68eca21d9d3e0d-environmental-campaigner-green-corps-atlanta</t>
+  </si>
+  <si>
+    <t>Pittsburgh, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/10e61b4e8822496ab2b1646b97926e21-environmental-campaigner-green-corps-pittsburgh</t>
+  </si>
+  <si>
+    <t>Executive Assistant - Recovery Services Bureau</t>
+  </si>
+  <si>
+    <t>Boston Public Health Commission</t>
+  </si>
+  <si>
+    <t>Health Medicine, Housing Homelessness, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca898b7794444b42a406289304ef63c9-executive-assistant-recovery-services-bureau-boston-public-health-commission-boston</t>
+  </si>
+  <si>
+    <t>Alliance for Innovation in Global Health</t>
+  </si>
+  <si>
+    <t>USD 205000.00 - 240000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bbdbab21317f4f6ca3c1e68a5929a15f-executive-director-alliance-for-innovation-in-global-health-san-francisco</t>
+  </si>
+  <si>
+    <t>Executive Director - Muddy Sneakers</t>
+  </si>
+  <si>
+    <t>Armstrong McGuire &amp; Associates</t>
+  </si>
+  <si>
+    <t>Raleigh, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/fb5a59b8aa564d3e84699c215d4e851f-executive-director-muddy-sneakers-armstrong-mcguire-associates-raleigh</t>
+  </si>
+  <si>
+    <t>Facilities Maintenance Technician</t>
+  </si>
+  <si>
+    <t>SAGE | Advocacy and Services for LGBT Elders, Inc.</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ae44ebbf49b44c529b7877e5e2e207fb-facilities-maintenance-technician-sage-advocacy-and-services-for-lgbt-elders-inc-new-york</t>
+  </si>
+  <si>
+    <t>Family Advocate of Family Enrichment Center</t>
+  </si>
+  <si>
+    <t>Children's Arts &amp; Science Workshops, Inc.</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/490e10a341db4a7382984122c8e86a52-family-advocate-of-family-enrichment-center-childrens-arts-science-workshops-inc-new-york</t>
+  </si>
+  <si>
+    <t>Finance &amp; Administration Manager</t>
+  </si>
+  <si>
+    <t>The Drama League</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/20c719f8b4724704aa684c941d60ed7d-finance-administration-manager-the-drama-league-new-york</t>
+  </si>
+  <si>
+    <t>Finance &amp; HR Associate</t>
+  </si>
+  <si>
+    <t>Nathan Cummings Foundation</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f63165f902047e99bf0a1e873cf5bdb-finance-hr-associate-nathan-cummings-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Finance Coordinator</t>
+  </si>
+  <si>
+    <t>New York Legal Assistance Group (NYLAG)</t>
+  </si>
+  <si>
+    <t>USD 82300.00 - 87320.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ed1f6dd6e02243e48079995bf0dbe2be-finance-coordinator-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Graphic Designer</t>
+  </si>
+  <si>
+    <t>U.S. Center for SafeSport</t>
+  </si>
+  <si>
+    <t>Remote (Colorado)</t>
+  </si>
+  <si>
+    <t>USD 26.82 - 29.17/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a49af641ec9042a5bfa3af5aa4cbc5aa-graphic-designer-us-center-for-safesport-denver</t>
+  </si>
+  <si>
+    <t>Housing Supervising Attorney</t>
+  </si>
+  <si>
+    <t>Bread for the City</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 103000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/35a6b2d9f6df4d67b4bd5e4a21a8a528-housing-supervising-attorney-bread-for-the-city-washington</t>
+  </si>
+  <si>
+    <t>Information Technology (IT) Associate, Level 2</t>
+  </si>
+  <si>
+    <t>The Bronx Defenders</t>
+  </si>
+  <si>
+    <t>Bronx, NY</t>
+  </si>
+  <si>
+    <t>USD 72100.00 - 73645.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9cfef126902f4e7590532f06029477cf-information-technology-it-associate-level-2-the-bronx-defenders-bronx</t>
+  </si>
+  <si>
+    <t>Information Technology Manager</t>
+  </si>
+  <si>
+    <t>Greater Boston Legal Services</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b7b41c126fd8479da60de48c5a3a849b-information-technology-manager-greater-boston-legal-services-boston</t>
+  </si>
+  <si>
+    <t>Inventory Manager</t>
+  </si>
+  <si>
+    <t>Baby2Baby</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7d1c383e14564ab4a3d769f135f66981-inventory-manager-baby2baby-los-angeles</t>
+  </si>
+  <si>
+    <t>Legal Data &amp; Grants Compliance Manager</t>
+  </si>
+  <si>
+    <t>USD 80340.00 - 104825.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c5aaaff46ac44a5ba3b906ad51fedd02-legal-data-grants-compliance-manager-asian-law-caucus-san-francisco</t>
+  </si>
+  <si>
+    <t>Managing Director - Hadassah Mid Atlantic</t>
+  </si>
+  <si>
+    <t>Hadassah, WZOA, Inc.</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Women, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/36b13a7ef6574f5eb205303dc272db8c-managing-director-hadassah-mid-atlantic-hadassah-wzoa-inc-new-york</t>
+  </si>
+  <si>
+    <t>Moderator and Curator: National Parks Virtual Speaker Series</t>
+  </si>
+  <si>
+    <t>Forum for Cultural Engagement</t>
+  </si>
+  <si>
+    <t>Education, International Relations, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d51f0851746d45408c4be9731dd8d44f-moderator-and-curator-national-parks-virtual-speaker-series-forum-for-cultural-engagement-washington</t>
+  </si>
+  <si>
+    <t>NYC Program Facilitator (Spanish Fluency Required)</t>
+  </si>
+  <si>
+    <t>Beyond Bedtime (formerly Pajama Program)</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de07f3a52f924c648caefdaf08b5219c-nyc-program-facilitator-spanish-fluency-required-beyond-bedtime-formerly-pajama-program-new-york</t>
+  </si>
+  <si>
+    <t>NYC Program Manager- Full Time</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a3d07a07f51547d089a8183103564065-nyc-program-manager-full-time-sadie-nash-leadership-project-new-york</t>
+  </si>
+  <si>
+    <t>Office Manager</t>
+  </si>
+  <si>
+    <t>Smithereen Farm</t>
+  </si>
+  <si>
+    <t>Pembroke, Maine</t>
+  </si>
+  <si>
+    <t>Agriculture, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/ac590830742e4cc78b69f8a83344a82f-office-manager-smithereen-farm-pembroke</t>
+  </si>
+  <si>
+    <t>Oncology Social Worker - Full-Time</t>
+  </si>
+  <si>
+    <t>Cancer Care, Inc.</t>
+  </si>
+  <si>
+    <t>Deer Park, New York</t>
+  </si>
+  <si>
+    <t>USD 67304.00 - 68334.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f254fc966868466b8c9025dde07a1455-oncology-social-worker-full-time-cancer-care-inc-deer-park</t>
+  </si>
+  <si>
+    <t>Oncology Social Worker - Part Time</t>
+  </si>
+  <si>
+    <t>USD 37.54 - 37.54/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7c420049643f4893a7b93420454ee377-oncology-social-worker-part-time-cancer-care-inc-new-york</t>
+  </si>
+  <si>
+    <t>OVS (Office of Victim Services) - Social Worker</t>
+  </si>
+  <si>
+    <t>Poughkeepsie, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1932c74ce3b64a8790cd4123ccbc40a2-ovs-office-of-victim-services-social-worker-legal-services-of-the-hudson-valley-poughkeepsie</t>
+  </si>
+  <si>
+    <t>OVS (Office of Victim Services) - Staff Attorney</t>
+  </si>
+  <si>
+    <t>Kingston, New York</t>
+  </si>
+  <si>
+    <t>USD 78850.00 - 145203.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7579d7b83f5f45b79d6041e87831a509-ovs-office-of-victim-services-staff-attorney-legal-services-of-the-hudson-valley-kingston</t>
+  </si>
+  <si>
+    <t>OVS (Office of Victim Services) Staff Attorney - Peekskill</t>
+  </si>
+  <si>
+    <t>Peekskill, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9b8e2c3f55d848339241772b91f83785-ovs-office-of-victim-services-staff-attorney-peekskill-legal-services-of-the-hudson-valley-peekskill</t>
+  </si>
+  <si>
+    <t>Parish Secretary</t>
+  </si>
+  <si>
+    <t>Immanuel Lutheran Church NYC</t>
+  </si>
+  <si>
+    <t>USD 22.00/hour</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/314bfd851a3046508ea2a50e3a095a1c-parish-secretary-immanuel-lutheran-church-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Program Director - Research and Strategic Initiatives</t>
+  </si>
+  <si>
+    <t>Verité</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/18de9b5811d145d0a1741a58feaf1b5a-program-director-research-and-strategic-initiatives-verite-amherst</t>
+  </si>
+  <si>
+    <t>Program Manager for Transit Policy</t>
+  </si>
+  <si>
+    <t>American Association of State Highway &amp; Transportation Officials</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f666d46acdd40fd99f9528937edf963-program-manager-for-transit-policy-american-association-of-state-highway-transportation-officials-washington</t>
+  </si>
+  <si>
+    <t>Program Officer, Outreach and Education</t>
+  </si>
+  <si>
+    <t>Chesapeake Bay Trust</t>
+  </si>
+  <si>
+    <t>Annapolis, Maryland</t>
+  </si>
+  <si>
+    <t>USD 64000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2f96cd5232e24b91be6797a14b656596-program-officer-outreach-and-education-chesapeake-bay-trust-annapolis</t>
+  </si>
+  <si>
+    <t>Project Coordinator</t>
+  </si>
+  <si>
+    <t>CAI</t>
+  </si>
+  <si>
+    <t>USD 66000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/869006d8b9df4ddea45a7923a26ca20d-project-coordinator-cai-new-york</t>
+  </si>
+  <si>
+    <t>Public Affairs Education Manager</t>
+  </si>
+  <si>
+    <t>Jewish Federation of Greater Houston</t>
+  </si>
+  <si>
+    <t>Houston, Texas</t>
+  </si>
+  <si>
+    <t>Education, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d1161e47cb341d0aa2d5efa8a61408a-public-affairs-education-manager-jewish-federation-of-greater-houston-houston</t>
+  </si>
+  <si>
+    <t>Re-entry Program Associate Position</t>
+  </si>
+  <si>
+    <t>Appellate Advocates</t>
+  </si>
+  <si>
+    <t>USD 69207.94 - 97036.27/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/27c0bb547b00435392596de09cc1b69b-re-entry-program-associate-position-appellate-advocates-new-york</t>
+  </si>
+  <si>
+    <t>Recruiter</t>
+  </si>
+  <si>
+    <t>Animal Care Centers of NYC</t>
+  </si>
+  <si>
+    <t>USD 29.80 - 29.80/hour</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/53c15ff37ad14f5da9505c7b095b5b0d-recruiter-animal-care-centers-of-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Residency Director</t>
+  </si>
+  <si>
+    <t>Millay Arts</t>
+  </si>
+  <si>
+    <t>Austerlitz, New York</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c48db3ed61444940b2446e894a23bb9c-residency-director-millay-arts-austerlitz</t>
+  </si>
+  <si>
+    <t>Resource Navigator - Part-Time</t>
+  </si>
+  <si>
+    <t>USD 28.29 - 28.29/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/75fc7e73e44144b0be910ae864502d29-resource-navigator-part-time-cancer-care-inc-new-york</t>
+  </si>
+  <si>
+    <t>Senior Manager of Digital Marketing</t>
+  </si>
+  <si>
+    <t>Keep America Beautiful, Inc.</t>
+  </si>
+  <si>
+    <t>USD 70000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb8c0747fce847f5b8e0f1181c852cbb-senior-manager-of-digital-marketing-keep-america-beautiful-inc-stamford</t>
+  </si>
+  <si>
+    <t>Special Assistant to the Executive Director &amp; COO</t>
+  </si>
+  <si>
+    <t>The DeBruce Foundation</t>
+  </si>
+  <si>
+    <t>Kansas City, Missouri</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/73d2d0d004e04003887c60ccc02331a7-special-assistant-to-the-executive-director-coo-the-debruce-foundation-kansas-city</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Legal Aid Bureau, Inc.</t>
+  </si>
+  <si>
+    <t>Frederick, Maryland</t>
+  </si>
+  <si>
+    <t>USD 79116.00 - 122122.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/520f1a36895a490bbff892fb727cac8c-staff-attorney-legal-aid-bureau-inc-frederick</t>
+  </si>
+  <si>
+    <t>USD 90262.00 - 100532.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c155374823504db48512bdfb05e8cd32-staff-attorney-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney - Domestic Violence/General Practice</t>
+  </si>
+  <si>
+    <t>Goshen, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/86e15ed6616e4f14bd85840f19477665-staff-attorney-domestic-violencegeneral-practice-legal-services-of-the-hudson-valley-goshen</t>
+  </si>
+  <si>
+    <t>Staff Attorney / Health Advocacy Fellow (2-year position)</t>
+  </si>
+  <si>
+    <t>USD 87994.00 - 104544.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1f31ec5134954e998af0b06379325345-staff-attorney-health-advocacy-fellow-2-year-position-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Systems &amp; Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Panorama Global</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7bd9a20500924ec8977ee2d525d581ed-systems-operations-coordinator-panorama-global-seattle</t>
+  </si>
+  <si>
+    <t>Tenant Organizer (Bilingual Spanish/English)</t>
+  </si>
+  <si>
+    <t>Tenants &amp; Neighbors</t>
+  </si>
+  <si>
+    <t>USD 52500.00 - 58500.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Civic Engagement, Communications Access</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ff576be79a5b4c85bea8f3873356a81c-tenant-organizer-bilingual-spanishenglish-tenants-neighbors-new-york</t>
+  </si>
+  <si>
+    <t>URGE: Western States Regional Policy &amp; Movement Building Director (OH or KS)</t>
+  </si>
+  <si>
+    <t>People Power (Talent Agency)</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/64f76de946a9433e92bc8bfe9fed79f9-urge-western-states-regional-policy-movement-building-director-oh-or-ks-people-power-talent-agency-oakland</t>
+  </si>
+  <si>
+    <t>Vice President, Advocacy</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/31b517c580cd4416bf97e892a95d0553-vice-president-advocacy-sakhi-for-south-asian-survivors-new-york</t>
+  </si>
+  <si>
+    <t>Vice President, Communications</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4421c6077cd843bd8d5ccef1f25b548a-vice-president-communications-sakhi-for-south-asian-survivors-new-york</t>
+  </si>
+  <si>
+    <t>Volunteers</t>
+  </si>
+  <si>
+    <t>The United Hope of Africa International (UHAI)</t>
+  </si>
+  <si>
+    <t>Nairobi, Nairobi, KE</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d3ec0f83a39c4f4e814151554cce5820-volunteers-the-united-hope-of-africa-international-uhai-nairobi</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d17eceaef284bc3bf3c7a4a3f879b05-volunteers-the-united-hope-of-africa-international-uhai-nairobi</t>
+  </si>
+  <si>
+    <t>Web Developer, eCRM</t>
+  </si>
+  <si>
+    <t>Humane World for Animals</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Disaster Relief, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e4d643910d8747ec80afbabaed10e9a3-web-developer-ecrm-humane-world-for-animals-washington</t>
+  </si>
+  <si>
+    <t>Workers' Rights Program Director</t>
+  </si>
+  <si>
+    <t>USD 161197.00 - 176144.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/23655c30663a4222b9675deaf5dcd3d0-workers-rights-program-director-asian-law-caucus-san-francisco</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +2223,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +2249,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2631,1378 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" t="s">
+        <v>67</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" t="s">
+        <v>67</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" t="s">
+        <v>92</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" t="s">
+        <v>98</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" t="s">
+        <v>104</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" t="s">
+        <v>38</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" t="s">
+        <v>114</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>119</v>
+      </c>
+      <c r="F25" t="s">
+        <v>120</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" t="s">
+        <v>125</v>
+      </c>
+      <c r="F26" t="s">
+        <v>126</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27" t="s">
+        <v>132</v>
+      </c>
+      <c r="F27" t="s">
+        <v>133</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C28" t="s">
+        <v>136</v>
+      </c>
+      <c r="D28" t="s">
+        <v>131</v>
+      </c>
+      <c r="E28" t="s">
+        <v>137</v>
+      </c>
+      <c r="F28" t="s">
+        <v>138</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>140</v>
+      </c>
+      <c r="B29" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" t="s">
+        <v>143</v>
+      </c>
+      <c r="F29" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" t="s">
+        <v>146</v>
+      </c>
+      <c r="C30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" t="s">
+        <v>148</v>
+      </c>
+      <c r="F30" t="s">
+        <v>149</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B31" t="s">
+        <v>152</v>
+      </c>
+      <c r="C31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" t="s">
+        <v>154</v>
+      </c>
+      <c r="F31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>156</v>
+      </c>
+      <c r="B32" t="s">
+        <v>157</v>
+      </c>
+      <c r="C32" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" t="s">
+        <v>159</v>
+      </c>
+      <c r="F32" t="s">
+        <v>160</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>162</v>
+      </c>
+      <c r="B33" t="s">
+        <v>157</v>
+      </c>
+      <c r="C33" t="s">
+        <v>163</v>
+      </c>
+      <c r="D33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" t="s">
+        <v>164</v>
+      </c>
+      <c r="F33" t="s">
+        <v>160</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>166</v>
+      </c>
+      <c r="B34" t="s">
+        <v>167</v>
+      </c>
+      <c r="C34" t="s">
+        <v>168</v>
+      </c>
+      <c r="D34" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34" t="s">
+        <v>169</v>
+      </c>
+      <c r="F34" t="s">
+        <v>170</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>172</v>
+      </c>
+      <c r="B35" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" t="s">
+        <v>173</v>
+      </c>
+      <c r="D35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" t="s">
+        <v>174</v>
+      </c>
+      <c r="F35" t="s">
+        <v>175</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>177</v>
+      </c>
+      <c r="B36" t="s">
+        <v>178</v>
+      </c>
+      <c r="C36" t="s">
+        <v>179</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>180</v>
+      </c>
+      <c r="F36" t="s">
+        <v>38</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>182</v>
+      </c>
+      <c r="B37" t="s">
+        <v>183</v>
+      </c>
+      <c r="C37" t="s">
+        <v>184</v>
+      </c>
+      <c r="D37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" t="s">
+        <v>185</v>
+      </c>
+      <c r="F37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>187</v>
+      </c>
+      <c r="B38" t="s">
+        <v>188</v>
+      </c>
+      <c r="C38" t="s">
+        <v>189</v>
+      </c>
+      <c r="D38" t="s">
+        <v>42</v>
+      </c>
+      <c r="E38" t="s">
+        <v>190</v>
+      </c>
+      <c r="F38" t="s">
+        <v>160</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>187</v>
+      </c>
+      <c r="B39" t="s">
+        <v>188</v>
+      </c>
+      <c r="C39" t="s">
+        <v>192</v>
+      </c>
+      <c r="D39" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" t="s">
+        <v>190</v>
+      </c>
+      <c r="F39" t="s">
+        <v>160</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>187</v>
+      </c>
+      <c r="B40" t="s">
+        <v>194</v>
+      </c>
+      <c r="C40" t="s">
+        <v>192</v>
+      </c>
+      <c r="D40" t="s">
+        <v>42</v>
+      </c>
+      <c r="E40" t="s">
+        <v>190</v>
+      </c>
+      <c r="F40" t="s">
+        <v>160</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>196</v>
+      </c>
+      <c r="B41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" t="s">
+        <v>197</v>
+      </c>
+      <c r="D41" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41" t="s">
+        <v>198</v>
+      </c>
+      <c r="F41" t="s">
+        <v>26</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>200</v>
+      </c>
+      <c r="B42" t="s">
+        <v>201</v>
+      </c>
+      <c r="C42" t="s">
+        <v>202</v>
+      </c>
+      <c r="D42" t="s">
+        <v>48</v>
+      </c>
+      <c r="E42" t="s">
+        <v>203</v>
+      </c>
+      <c r="F42" t="s">
+        <v>86</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>205</v>
+      </c>
+      <c r="B43" t="s">
+        <v>206</v>
+      </c>
+      <c r="C43" t="s">
+        <v>207</v>
+      </c>
+      <c r="D43" t="s">
+        <v>48</v>
+      </c>
+      <c r="E43" t="s">
+        <v>208</v>
+      </c>
+      <c r="F43" t="s">
+        <v>209</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>211</v>
+      </c>
+      <c r="B44" t="s">
+        <v>141</v>
+      </c>
+      <c r="C44" t="s">
+        <v>142</v>
+      </c>
+      <c r="D44" t="s">
+        <v>48</v>
+      </c>
+      <c r="E44" t="s">
+        <v>212</v>
+      </c>
+      <c r="F44" t="s">
+        <v>213</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>215</v>
+      </c>
+      <c r="B45" t="s">
+        <v>216</v>
+      </c>
+      <c r="C45" t="s">
+        <v>217</v>
+      </c>
+      <c r="D45" t="s">
+        <v>48</v>
+      </c>
+      <c r="E45" t="s">
+        <v>218</v>
+      </c>
+      <c r="F45" t="s">
+        <v>219</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>221</v>
+      </c>
+      <c r="B46" t="s">
+        <v>222</v>
+      </c>
+      <c r="C46" t="s">
+        <v>223</v>
+      </c>
+      <c r="D46" t="s">
+        <v>48</v>
+      </c>
+      <c r="E46" t="s">
+        <v>224</v>
+      </c>
+      <c r="F46" t="s">
+        <v>225</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>227</v>
+      </c>
+      <c r="B47" t="s">
+        <v>228</v>
+      </c>
+      <c r="C47" t="s">
+        <v>229</v>
+      </c>
+      <c r="D47" t="s">
+        <v>48</v>
+      </c>
+      <c r="E47" t="s">
+        <v>230</v>
+      </c>
+      <c r="F47" t="s">
+        <v>231</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>233</v>
+      </c>
+      <c r="B48" t="s">
+        <v>234</v>
+      </c>
+      <c r="C48" t="s">
+        <v>235</v>
+      </c>
+      <c r="D48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E48" t="s">
+        <v>236</v>
+      </c>
+      <c r="F48" t="s">
+        <v>237</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>239</v>
+      </c>
+      <c r="B49" t="s">
+        <v>240</v>
+      </c>
+      <c r="C49" t="s">
+        <v>241</v>
+      </c>
+      <c r="D49" t="s">
+        <v>42</v>
+      </c>
+      <c r="E49" t="s">
+        <v>242</v>
+      </c>
+      <c r="F49" t="s">
+        <v>243</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>245</v>
+      </c>
+      <c r="B50" t="s">
+        <v>240</v>
+      </c>
+      <c r="C50" t="s">
+        <v>241</v>
+      </c>
+      <c r="D50" t="s">
+        <v>42</v>
+      </c>
+      <c r="E50" t="s">
+        <v>242</v>
+      </c>
+      <c r="F50" t="s">
+        <v>38</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>247</v>
+      </c>
+      <c r="B51" t="s">
+        <v>240</v>
+      </c>
+      <c r="C51" t="s">
+        <v>248</v>
+      </c>
+      <c r="D51" t="s">
+        <v>42</v>
+      </c>
+      <c r="E51" t="s">
+        <v>242</v>
+      </c>
+      <c r="F51" t="s">
+        <v>38</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>250</v>
+      </c>
+      <c r="B52" t="s">
+        <v>240</v>
+      </c>
+      <c r="C52" t="s">
+        <v>251</v>
+      </c>
+      <c r="D52" t="s">
+        <v>42</v>
+      </c>
+      <c r="E52" t="s">
+        <v>252</v>
+      </c>
+      <c r="F52" t="s">
+        <v>38</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>254</v>
+      </c>
+      <c r="B53" t="s">
+        <v>255</v>
+      </c>
+      <c r="C53" t="s">
+        <v>256</v>
+      </c>
+      <c r="D53" t="s">
+        <v>48</v>
+      </c>
+      <c r="E53" t="s">
+        <v>257</v>
+      </c>
+      <c r="F53" t="s">
+        <v>258</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>260</v>
+      </c>
+      <c r="B54" t="s">
+        <v>35</v>
+      </c>
+      <c r="C54" t="s">
+        <v>41</v>
+      </c>
+      <c r="D54" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F54" t="s">
+        <v>38</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>262</v>
+      </c>
+      <c r="B55" t="s">
+        <v>35</v>
+      </c>
+      <c r="C55" t="s">
+        <v>36</v>
+      </c>
+      <c r="D55" t="s">
+        <v>42</v>
+      </c>
+      <c r="E55" t="s">
+        <v>43</v>
+      </c>
+      <c r="F55" t="s">
+        <v>38</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>264</v>
+      </c>
+      <c r="B56" t="s">
+        <v>265</v>
+      </c>
+      <c r="C56" t="s">
+        <v>266</v>
+      </c>
+      <c r="D56" t="s">
+        <v>48</v>
+      </c>
+      <c r="E56" t="s">
+        <v>267</v>
+      </c>
+      <c r="F56" t="s">
+        <v>268</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>270</v>
+      </c>
+      <c r="B57" t="s">
+        <v>271</v>
+      </c>
+      <c r="C57" t="s">
+        <v>272</v>
+      </c>
+      <c r="D57" t="s">
+        <v>42</v>
+      </c>
+      <c r="E57" t="s">
+        <v>273</v>
+      </c>
+      <c r="F57" t="s">
+        <v>13</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>275</v>
+      </c>
+      <c r="B58" t="s">
+        <v>276</v>
+      </c>
+      <c r="C58" t="s">
+        <v>277</v>
+      </c>
+      <c r="D58" t="s">
+        <v>42</v>
+      </c>
+      <c r="E58" t="s">
+        <v>278</v>
+      </c>
+      <c r="F58" t="s">
+        <v>279</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +4058,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +4097,2434 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F2" t="s">
+        <v>286</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E3" t="s">
+        <v>292</v>
+      </c>
+      <c r="F3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D4" t="s">
+        <v>291</v>
+      </c>
+      <c r="E4" t="s">
+        <v>298</v>
+      </c>
+      <c r="F4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F5" t="s">
+        <v>305</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>307</v>
+      </c>
+      <c r="B6" t="s">
+        <v>308</v>
+      </c>
+      <c r="C6" t="s">
+        <v>309</v>
+      </c>
+      <c r="D6" t="s">
+        <v>291</v>
+      </c>
+      <c r="E6" t="s">
+        <v>310</v>
+      </c>
+      <c r="F6" t="s">
+        <v>311</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B7" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" t="s">
+        <v>303</v>
+      </c>
+      <c r="D7" t="s">
+        <v>315</v>
+      </c>
+      <c r="E7" t="s">
+        <v>316</v>
+      </c>
+      <c r="F7" t="s">
+        <v>317</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>319</v>
+      </c>
+      <c r="B8" t="s">
+        <v>320</v>
+      </c>
+      <c r="C8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D8" t="s">
+        <v>284</v>
+      </c>
+      <c r="E8" t="s">
+        <v>322</v>
+      </c>
+      <c r="F8" t="s">
+        <v>323</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B9" t="s">
+        <v>320</v>
+      </c>
+      <c r="C9" t="s">
+        <v>321</v>
+      </c>
+      <c r="D9" t="s">
+        <v>284</v>
+      </c>
+      <c r="E9" t="s">
+        <v>322</v>
+      </c>
+      <c r="F9" t="s">
+        <v>323</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>327</v>
+      </c>
+      <c r="B10" t="s">
+        <v>320</v>
+      </c>
+      <c r="C10" t="s">
+        <v>321</v>
+      </c>
+      <c r="D10" t="s">
+        <v>284</v>
+      </c>
+      <c r="E10" t="s">
+        <v>322</v>
+      </c>
+      <c r="F10" t="s">
+        <v>323</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>329</v>
+      </c>
+      <c r="B11" t="s">
+        <v>330</v>
+      </c>
+      <c r="C11" t="s">
+        <v>331</v>
+      </c>
+      <c r="D11" t="s">
+        <v>315</v>
+      </c>
+      <c r="E11" t="s">
+        <v>285</v>
+      </c>
+      <c r="F11" t="s">
+        <v>332</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>334</v>
+      </c>
+      <c r="B12" t="s">
+        <v>335</v>
+      </c>
+      <c r="C12" t="s">
+        <v>303</v>
+      </c>
+      <c r="D12" t="s">
+        <v>315</v>
+      </c>
+      <c r="E12" t="s">
+        <v>336</v>
+      </c>
+      <c r="F12" t="s">
+        <v>337</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>339</v>
+      </c>
+      <c r="B13" t="s">
+        <v>340</v>
+      </c>
+      <c r="C13" t="s">
+        <v>341</v>
+      </c>
+      <c r="D13" t="s">
+        <v>315</v>
+      </c>
+      <c r="E13" t="s">
+        <v>342</v>
+      </c>
+      <c r="F13" t="s">
+        <v>343</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>345</v>
+      </c>
+      <c r="B14" t="s">
+        <v>346</v>
+      </c>
+      <c r="C14" t="s">
+        <v>347</v>
+      </c>
+      <c r="D14" t="s">
+        <v>315</v>
+      </c>
+      <c r="E14" t="s">
+        <v>348</v>
+      </c>
+      <c r="F14" t="s">
+        <v>349</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>351</v>
+      </c>
+      <c r="B15" t="s">
+        <v>352</v>
+      </c>
+      <c r="C15" t="s">
+        <v>303</v>
+      </c>
+      <c r="D15" t="s">
+        <v>315</v>
+      </c>
+      <c r="E15" t="s">
+        <v>353</v>
+      </c>
+      <c r="F15" t="s">
+        <v>354</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>356</v>
+      </c>
+      <c r="B16" t="s">
+        <v>357</v>
+      </c>
+      <c r="C16" t="s">
+        <v>358</v>
+      </c>
+      <c r="D16" t="s">
+        <v>315</v>
+      </c>
+      <c r="E16" t="s">
+        <v>359</v>
+      </c>
+      <c r="F16" t="s">
+        <v>360</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>362</v>
+      </c>
+      <c r="B17" t="s">
+        <v>363</v>
+      </c>
+      <c r="C17" t="s">
+        <v>309</v>
+      </c>
+      <c r="D17" t="s">
+        <v>291</v>
+      </c>
+      <c r="E17" t="s">
+        <v>285</v>
+      </c>
+      <c r="F17" t="s">
+        <v>364</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>366</v>
+      </c>
+      <c r="B18" t="s">
+        <v>367</v>
+      </c>
+      <c r="C18" t="s">
+        <v>368</v>
+      </c>
+      <c r="D18" t="s">
+        <v>315</v>
+      </c>
+      <c r="E18" t="s">
+        <v>369</v>
+      </c>
+      <c r="F18" t="s">
+        <v>370</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>372</v>
+      </c>
+      <c r="B19" t="s">
+        <v>373</v>
+      </c>
+      <c r="C19" t="s">
+        <v>374</v>
+      </c>
+      <c r="D19" t="s">
+        <v>291</v>
+      </c>
+      <c r="E19" t="s">
+        <v>375</v>
+      </c>
+      <c r="F19" t="s">
+        <v>376</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>378</v>
+      </c>
+      <c r="B20" t="s">
+        <v>379</v>
+      </c>
+      <c r="C20" t="s">
+        <v>380</v>
+      </c>
+      <c r="D20" t="s">
+        <v>315</v>
+      </c>
+      <c r="E20" t="s">
+        <v>381</v>
+      </c>
+      <c r="F20" t="s">
+        <v>382</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>384</v>
+      </c>
+      <c r="B21" t="s">
+        <v>385</v>
+      </c>
+      <c r="C21" t="s">
+        <v>386</v>
+      </c>
+      <c r="D21" t="s">
+        <v>315</v>
+      </c>
+      <c r="E21" t="s">
+        <v>387</v>
+      </c>
+      <c r="F21" t="s">
+        <v>388</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>390</v>
+      </c>
+      <c r="B22" t="s">
+        <v>391</v>
+      </c>
+      <c r="C22" t="s">
+        <v>309</v>
+      </c>
+      <c r="D22" t="s">
+        <v>315</v>
+      </c>
+      <c r="E22" t="s">
+        <v>392</v>
+      </c>
+      <c r="F22" t="s">
+        <v>393</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>395</v>
+      </c>
+      <c r="B23" t="s">
+        <v>396</v>
+      </c>
+      <c r="C23" t="s">
+        <v>397</v>
+      </c>
+      <c r="D23" t="s">
+        <v>398</v>
+      </c>
+      <c r="E23" t="s">
+        <v>399</v>
+      </c>
+      <c r="F23" t="s">
+        <v>400</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>402</v>
+      </c>
+      <c r="B24" t="s">
+        <v>403</v>
+      </c>
+      <c r="C24" t="s">
+        <v>404</v>
+      </c>
+      <c r="D24" t="s">
+        <v>315</v>
+      </c>
+      <c r="E24" t="s">
+        <v>405</v>
+      </c>
+      <c r="F24" t="s">
+        <v>406</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>402</v>
+      </c>
+      <c r="B25" t="s">
+        <v>408</v>
+      </c>
+      <c r="C25" t="s">
+        <v>303</v>
+      </c>
+      <c r="D25" t="s">
+        <v>315</v>
+      </c>
+      <c r="E25" t="s">
+        <v>409</v>
+      </c>
+      <c r="F25" t="s">
+        <v>410</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>412</v>
+      </c>
+      <c r="B26" t="s">
+        <v>413</v>
+      </c>
+      <c r="C26" t="s">
+        <v>290</v>
+      </c>
+      <c r="D26" t="s">
+        <v>315</v>
+      </c>
+      <c r="E26" t="s">
+        <v>414</v>
+      </c>
+      <c r="F26" t="s">
+        <v>415</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>417</v>
+      </c>
+      <c r="B27" t="s">
+        <v>418</v>
+      </c>
+      <c r="C27" t="s">
+        <v>419</v>
+      </c>
+      <c r="D27" t="s">
+        <v>315</v>
+      </c>
+      <c r="E27" t="s">
+        <v>420</v>
+      </c>
+      <c r="F27" t="s">
+        <v>421</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>423</v>
+      </c>
+      <c r="B28" t="s">
+        <v>424</v>
+      </c>
+      <c r="C28" t="s">
+        <v>425</v>
+      </c>
+      <c r="D28" t="s">
+        <v>315</v>
+      </c>
+      <c r="E28" t="s">
+        <v>426</v>
+      </c>
+      <c r="F28" t="s">
+        <v>427</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>429</v>
+      </c>
+      <c r="B29" t="s">
+        <v>430</v>
+      </c>
+      <c r="C29" t="s">
+        <v>303</v>
+      </c>
+      <c r="D29" t="s">
+        <v>284</v>
+      </c>
+      <c r="E29" t="s">
+        <v>322</v>
+      </c>
+      <c r="F29" t="s">
+        <v>431</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>433</v>
+      </c>
+      <c r="B30" t="s">
+        <v>285</v>
+      </c>
+      <c r="C30" t="s">
+        <v>434</v>
+      </c>
+      <c r="D30" t="s">
+        <v>315</v>
+      </c>
+      <c r="E30" t="s">
+        <v>435</v>
+      </c>
+      <c r="F30" t="s">
+        <v>285</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>437</v>
+      </c>
+      <c r="B31" t="s">
+        <v>438</v>
+      </c>
+      <c r="C31" t="s">
+        <v>207</v>
+      </c>
+      <c r="D31" t="s">
+        <v>315</v>
+      </c>
+      <c r="E31" t="s">
+        <v>439</v>
+      </c>
+      <c r="F31" t="s">
+        <v>440</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>442</v>
+      </c>
+      <c r="B32" t="s">
+        <v>443</v>
+      </c>
+      <c r="C32" t="s">
+        <v>425</v>
+      </c>
+      <c r="D32" t="s">
+        <v>315</v>
+      </c>
+      <c r="E32" t="s">
+        <v>353</v>
+      </c>
+      <c r="F32" t="s">
+        <v>444</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>446</v>
+      </c>
+      <c r="B33" t="s">
+        <v>447</v>
+      </c>
+      <c r="C33" t="s">
+        <v>448</v>
+      </c>
+      <c r="D33" t="s">
+        <v>315</v>
+      </c>
+      <c r="E33" t="s">
+        <v>449</v>
+      </c>
+      <c r="F33" t="s">
+        <v>450</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>452</v>
+      </c>
+      <c r="B34" t="s">
+        <v>453</v>
+      </c>
+      <c r="C34" t="s">
+        <v>309</v>
+      </c>
+      <c r="D34" t="s">
+        <v>315</v>
+      </c>
+      <c r="E34" t="s">
+        <v>454</v>
+      </c>
+      <c r="F34" t="s">
+        <v>455</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>457</v>
+      </c>
+      <c r="B35" t="s">
+        <v>458</v>
+      </c>
+      <c r="C35" t="s">
+        <v>303</v>
+      </c>
+      <c r="D35" t="s">
+        <v>315</v>
+      </c>
+      <c r="E35" t="s">
+        <v>459</v>
+      </c>
+      <c r="F35" t="s">
+        <v>460</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>462</v>
+      </c>
+      <c r="B36" t="s">
+        <v>463</v>
+      </c>
+      <c r="C36" t="s">
+        <v>464</v>
+      </c>
+      <c r="D36" t="s">
+        <v>315</v>
+      </c>
+      <c r="E36" t="s">
+        <v>336</v>
+      </c>
+      <c r="F36" t="s">
+        <v>465</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>462</v>
+      </c>
+      <c r="B37" t="s">
+        <v>463</v>
+      </c>
+      <c r="C37" t="s">
+        <v>303</v>
+      </c>
+      <c r="D37" t="s">
+        <v>315</v>
+      </c>
+      <c r="E37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F37" t="s">
+        <v>465</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>468</v>
+      </c>
+      <c r="B38" t="s">
+        <v>469</v>
+      </c>
+      <c r="C38" t="s">
+        <v>470</v>
+      </c>
+      <c r="D38" t="s">
+        <v>315</v>
+      </c>
+      <c r="E38" t="s">
+        <v>471</v>
+      </c>
+      <c r="F38" t="s">
+        <v>472</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>468</v>
+      </c>
+      <c r="B39" t="s">
+        <v>474</v>
+      </c>
+      <c r="C39" t="s">
+        <v>475</v>
+      </c>
+      <c r="D39" t="s">
+        <v>315</v>
+      </c>
+      <c r="E39" t="s">
+        <v>476</v>
+      </c>
+      <c r="F39" t="s">
+        <v>477</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>479</v>
+      </c>
+      <c r="B40" t="s">
+        <v>346</v>
+      </c>
+      <c r="C40" t="s">
+        <v>480</v>
+      </c>
+      <c r="D40" t="s">
+        <v>315</v>
+      </c>
+      <c r="E40" t="s">
+        <v>481</v>
+      </c>
+      <c r="F40" t="s">
+        <v>349</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>483</v>
+      </c>
+      <c r="B41" t="s">
+        <v>484</v>
+      </c>
+      <c r="C41" t="s">
+        <v>309</v>
+      </c>
+      <c r="D41" t="s">
+        <v>284</v>
+      </c>
+      <c r="E41" t="s">
+        <v>285</v>
+      </c>
+      <c r="F41" t="s">
+        <v>485</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>487</v>
+      </c>
+      <c r="B42" t="s">
+        <v>488</v>
+      </c>
+      <c r="C42" t="s">
+        <v>368</v>
+      </c>
+      <c r="D42" t="s">
+        <v>315</v>
+      </c>
+      <c r="E42" t="s">
+        <v>489</v>
+      </c>
+      <c r="F42" t="s">
+        <v>285</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>491</v>
+      </c>
+      <c r="B43" t="s">
+        <v>492</v>
+      </c>
+      <c r="C43" t="s">
+        <v>493</v>
+      </c>
+      <c r="D43" t="s">
+        <v>315</v>
+      </c>
+      <c r="E43" t="s">
+        <v>494</v>
+      </c>
+      <c r="F43" t="s">
+        <v>495</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>497</v>
+      </c>
+      <c r="B44" t="s">
+        <v>498</v>
+      </c>
+      <c r="C44" t="s">
+        <v>499</v>
+      </c>
+      <c r="D44" t="s">
+        <v>315</v>
+      </c>
+      <c r="E44" t="s">
+        <v>500</v>
+      </c>
+      <c r="F44" t="s">
+        <v>501</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>497</v>
+      </c>
+      <c r="B45" t="s">
+        <v>498</v>
+      </c>
+      <c r="C45" t="s">
+        <v>503</v>
+      </c>
+      <c r="D45" t="s">
+        <v>315</v>
+      </c>
+      <c r="E45" t="s">
+        <v>500</v>
+      </c>
+      <c r="F45" t="s">
+        <v>501</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>497</v>
+      </c>
+      <c r="B46" t="s">
+        <v>498</v>
+      </c>
+      <c r="C46" t="s">
+        <v>505</v>
+      </c>
+      <c r="D46" t="s">
+        <v>315</v>
+      </c>
+      <c r="E46" t="s">
+        <v>500</v>
+      </c>
+      <c r="F46" t="s">
+        <v>501</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>497</v>
+      </c>
+      <c r="B47" t="s">
+        <v>498</v>
+      </c>
+      <c r="C47" t="s">
+        <v>493</v>
+      </c>
+      <c r="D47" t="s">
+        <v>315</v>
+      </c>
+      <c r="E47" t="s">
+        <v>500</v>
+      </c>
+      <c r="F47" t="s">
+        <v>501</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>497</v>
+      </c>
+      <c r="B48" t="s">
+        <v>498</v>
+      </c>
+      <c r="C48" t="s">
+        <v>425</v>
+      </c>
+      <c r="D48" t="s">
+        <v>315</v>
+      </c>
+      <c r="E48" t="s">
+        <v>500</v>
+      </c>
+      <c r="F48" t="s">
+        <v>501</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>497</v>
+      </c>
+      <c r="B49" t="s">
+        <v>498</v>
+      </c>
+      <c r="C49" t="s">
+        <v>509</v>
+      </c>
+      <c r="D49" t="s">
+        <v>315</v>
+      </c>
+      <c r="E49" t="s">
+        <v>500</v>
+      </c>
+      <c r="F49" t="s">
+        <v>501</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>497</v>
+      </c>
+      <c r="B50" t="s">
+        <v>498</v>
+      </c>
+      <c r="C50" t="s">
+        <v>511</v>
+      </c>
+      <c r="D50" t="s">
+        <v>315</v>
+      </c>
+      <c r="E50" t="s">
+        <v>500</v>
+      </c>
+      <c r="F50" t="s">
+        <v>501</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>497</v>
+      </c>
+      <c r="B51" t="s">
+        <v>498</v>
+      </c>
+      <c r="C51" t="s">
+        <v>297</v>
+      </c>
+      <c r="D51" t="s">
+        <v>315</v>
+      </c>
+      <c r="E51" t="s">
+        <v>500</v>
+      </c>
+      <c r="F51" t="s">
+        <v>501</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>497</v>
+      </c>
+      <c r="B52" t="s">
+        <v>498</v>
+      </c>
+      <c r="C52" t="s">
+        <v>514</v>
+      </c>
+      <c r="D52" t="s">
+        <v>315</v>
+      </c>
+      <c r="E52" t="s">
+        <v>500</v>
+      </c>
+      <c r="F52" t="s">
+        <v>501</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>497</v>
+      </c>
+      <c r="B53" t="s">
+        <v>498</v>
+      </c>
+      <c r="C53" t="s">
+        <v>516</v>
+      </c>
+      <c r="D53" t="s">
+        <v>315</v>
+      </c>
+      <c r="E53" t="s">
+        <v>500</v>
+      </c>
+      <c r="F53" t="s">
+        <v>501</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>518</v>
+      </c>
+      <c r="B54" t="s">
+        <v>519</v>
+      </c>
+      <c r="C54" t="s">
+        <v>297</v>
+      </c>
+      <c r="D54" t="s">
+        <v>315</v>
+      </c>
+      <c r="E54" t="s">
+        <v>449</v>
+      </c>
+      <c r="F54" t="s">
+        <v>520</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>88</v>
+      </c>
+      <c r="B55" t="s">
+        <v>522</v>
+      </c>
+      <c r="C55" t="s">
+        <v>309</v>
+      </c>
+      <c r="D55" t="s">
+        <v>315</v>
+      </c>
+      <c r="E55" t="s">
+        <v>523</v>
+      </c>
+      <c r="F55" t="s">
+        <v>524</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>526</v>
+      </c>
+      <c r="B56" t="s">
+        <v>527</v>
+      </c>
+      <c r="C56" t="s">
+        <v>528</v>
+      </c>
+      <c r="D56" t="s">
+        <v>315</v>
+      </c>
+      <c r="E56" t="s">
+        <v>529</v>
+      </c>
+      <c r="F56" t="s">
+        <v>530</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>532</v>
+      </c>
+      <c r="B57" t="s">
+        <v>533</v>
+      </c>
+      <c r="C57" t="s">
+        <v>303</v>
+      </c>
+      <c r="D57" t="s">
+        <v>315</v>
+      </c>
+      <c r="E57" t="s">
+        <v>534</v>
+      </c>
+      <c r="F57" t="s">
+        <v>535</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>537</v>
+      </c>
+      <c r="B58" t="s">
+        <v>538</v>
+      </c>
+      <c r="C58" t="s">
+        <v>303</v>
+      </c>
+      <c r="D58" t="s">
+        <v>315</v>
+      </c>
+      <c r="E58" t="s">
+        <v>449</v>
+      </c>
+      <c r="F58" t="s">
+        <v>539</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>541</v>
+      </c>
+      <c r="B59" t="s">
+        <v>542</v>
+      </c>
+      <c r="C59" t="s">
+        <v>303</v>
+      </c>
+      <c r="D59" t="s">
+        <v>315</v>
+      </c>
+      <c r="E59" t="s">
+        <v>543</v>
+      </c>
+      <c r="F59" t="s">
+        <v>544</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>546</v>
+      </c>
+      <c r="B60" t="s">
+        <v>547</v>
+      </c>
+      <c r="C60" t="s">
+        <v>303</v>
+      </c>
+      <c r="D60" t="s">
+        <v>315</v>
+      </c>
+      <c r="E60" t="s">
+        <v>548</v>
+      </c>
+      <c r="F60" t="s">
+        <v>549</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>551</v>
+      </c>
+      <c r="B61" t="s">
+        <v>552</v>
+      </c>
+      <c r="C61" t="s">
+        <v>303</v>
+      </c>
+      <c r="D61" t="s">
+        <v>315</v>
+      </c>
+      <c r="E61" t="s">
+        <v>553</v>
+      </c>
+      <c r="F61" t="s">
+        <v>421</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>555</v>
+      </c>
+      <c r="B62" t="s">
+        <v>556</v>
+      </c>
+      <c r="C62" t="s">
+        <v>557</v>
+      </c>
+      <c r="D62" t="s">
+        <v>315</v>
+      </c>
+      <c r="E62" t="s">
+        <v>558</v>
+      </c>
+      <c r="F62" t="s">
+        <v>559</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>561</v>
+      </c>
+      <c r="B63" t="s">
+        <v>562</v>
+      </c>
+      <c r="C63" t="s">
+        <v>207</v>
+      </c>
+      <c r="D63" t="s">
+        <v>315</v>
+      </c>
+      <c r="E63" t="s">
+        <v>563</v>
+      </c>
+      <c r="F63" t="s">
+        <v>564</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>566</v>
+      </c>
+      <c r="B64" t="s">
+        <v>567</v>
+      </c>
+      <c r="C64" t="s">
+        <v>568</v>
+      </c>
+      <c r="D64" t="s">
+        <v>315</v>
+      </c>
+      <c r="E64" t="s">
+        <v>569</v>
+      </c>
+      <c r="F64" t="s">
+        <v>570</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>572</v>
+      </c>
+      <c r="B65" t="s">
+        <v>573</v>
+      </c>
+      <c r="C65" t="s">
+        <v>297</v>
+      </c>
+      <c r="D65" t="s">
+        <v>315</v>
+      </c>
+      <c r="E65" t="s">
+        <v>574</v>
+      </c>
+      <c r="F65" t="s">
+        <v>421</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>576</v>
+      </c>
+      <c r="B66" t="s">
+        <v>577</v>
+      </c>
+      <c r="C66" t="s">
+        <v>503</v>
+      </c>
+      <c r="D66" t="s">
+        <v>315</v>
+      </c>
+      <c r="E66" t="s">
+        <v>578</v>
+      </c>
+      <c r="F66" t="s">
+        <v>293</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>580</v>
+      </c>
+      <c r="B67" t="s">
+        <v>413</v>
+      </c>
+      <c r="C67" t="s">
+        <v>290</v>
+      </c>
+      <c r="D67" t="s">
+        <v>315</v>
+      </c>
+      <c r="E67" t="s">
+        <v>581</v>
+      </c>
+      <c r="F67" t="s">
+        <v>415</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>583</v>
+      </c>
+      <c r="B68" t="s">
+        <v>584</v>
+      </c>
+      <c r="C68" t="s">
+        <v>309</v>
+      </c>
+      <c r="D68" t="s">
+        <v>315</v>
+      </c>
+      <c r="E68" t="s">
+        <v>585</v>
+      </c>
+      <c r="F68" t="s">
+        <v>586</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>588</v>
+      </c>
+      <c r="B69" t="s">
+        <v>589</v>
+      </c>
+      <c r="C69" t="s">
+        <v>309</v>
+      </c>
+      <c r="D69" t="s">
+        <v>284</v>
+      </c>
+      <c r="E69" t="s">
+        <v>285</v>
+      </c>
+      <c r="F69" t="s">
+        <v>590</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>592</v>
+      </c>
+      <c r="B70" t="s">
+        <v>593</v>
+      </c>
+      <c r="C70" t="s">
+        <v>303</v>
+      </c>
+      <c r="D70" t="s">
+        <v>291</v>
+      </c>
+      <c r="E70" t="s">
+        <v>594</v>
+      </c>
+      <c r="F70" t="s">
+        <v>286</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>596</v>
+      </c>
+      <c r="B71" t="s">
+        <v>463</v>
+      </c>
+      <c r="C71" t="s">
+        <v>303</v>
+      </c>
+      <c r="D71" t="s">
+        <v>315</v>
+      </c>
+      <c r="E71" t="s">
+        <v>597</v>
+      </c>
+      <c r="F71" t="s">
+        <v>465</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>599</v>
+      </c>
+      <c r="B72" t="s">
+        <v>600</v>
+      </c>
+      <c r="C72" t="s">
+        <v>601</v>
+      </c>
+      <c r="D72" t="s">
+        <v>291</v>
+      </c>
+      <c r="E72" t="s">
+        <v>310</v>
+      </c>
+      <c r="F72" t="s">
+        <v>602</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>604</v>
+      </c>
+      <c r="B73" t="s">
+        <v>605</v>
+      </c>
+      <c r="C73" t="s">
+        <v>606</v>
+      </c>
+      <c r="D73" t="s">
+        <v>315</v>
+      </c>
+      <c r="E73" t="s">
+        <v>607</v>
+      </c>
+      <c r="F73" t="s">
+        <v>608</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>610</v>
+      </c>
+      <c r="B74" t="s">
+        <v>605</v>
+      </c>
+      <c r="C74" t="s">
+        <v>303</v>
+      </c>
+      <c r="D74" t="s">
+        <v>291</v>
+      </c>
+      <c r="E74" t="s">
+        <v>611</v>
+      </c>
+      <c r="F74" t="s">
+        <v>524</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>613</v>
+      </c>
+      <c r="B75" t="s">
+        <v>346</v>
+      </c>
+      <c r="C75" t="s">
+        <v>614</v>
+      </c>
+      <c r="D75" t="s">
+        <v>315</v>
+      </c>
+      <c r="E75" t="s">
+        <v>615</v>
+      </c>
+      <c r="F75" t="s">
+        <v>349</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>617</v>
+      </c>
+      <c r="B76" t="s">
+        <v>346</v>
+      </c>
+      <c r="C76" t="s">
+        <v>618</v>
+      </c>
+      <c r="D76" t="s">
+        <v>315</v>
+      </c>
+      <c r="E76" t="s">
+        <v>619</v>
+      </c>
+      <c r="F76" t="s">
+        <v>349</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>621</v>
+      </c>
+      <c r="B77" t="s">
+        <v>346</v>
+      </c>
+      <c r="C77" t="s">
+        <v>622</v>
+      </c>
+      <c r="D77" t="s">
+        <v>315</v>
+      </c>
+      <c r="E77" t="s">
+        <v>619</v>
+      </c>
+      <c r="F77" t="s">
+        <v>349</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>624</v>
+      </c>
+      <c r="B78" t="s">
+        <v>625</v>
+      </c>
+      <c r="C78" t="s">
+        <v>303</v>
+      </c>
+      <c r="D78" t="s">
+        <v>291</v>
+      </c>
+      <c r="E78" t="s">
+        <v>626</v>
+      </c>
+      <c r="F78" t="s">
+        <v>627</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>629</v>
+      </c>
+      <c r="B79" t="s">
+        <v>630</v>
+      </c>
+      <c r="C79" t="s">
+        <v>309</v>
+      </c>
+      <c r="D79" t="s">
+        <v>315</v>
+      </c>
+      <c r="E79" t="s">
+        <v>631</v>
+      </c>
+      <c r="F79" t="s">
+        <v>632</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>634</v>
+      </c>
+      <c r="B80" t="s">
+        <v>635</v>
+      </c>
+      <c r="C80" t="s">
+        <v>636</v>
+      </c>
+      <c r="D80" t="s">
+        <v>315</v>
+      </c>
+      <c r="E80" t="s">
+        <v>637</v>
+      </c>
+      <c r="F80" t="s">
+        <v>638</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>640</v>
+      </c>
+      <c r="B81" t="s">
+        <v>641</v>
+      </c>
+      <c r="C81" t="s">
+        <v>642</v>
+      </c>
+      <c r="D81" t="s">
+        <v>315</v>
+      </c>
+      <c r="E81" t="s">
+        <v>643</v>
+      </c>
+      <c r="F81" t="s">
+        <v>644</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>646</v>
+      </c>
+      <c r="B82" t="s">
+        <v>647</v>
+      </c>
+      <c r="C82" t="s">
+        <v>303</v>
+      </c>
+      <c r="D82" t="s">
+        <v>315</v>
+      </c>
+      <c r="E82" t="s">
+        <v>648</v>
+      </c>
+      <c r="F82" t="s">
+        <v>649</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>651</v>
+      </c>
+      <c r="B83" t="s">
+        <v>652</v>
+      </c>
+      <c r="C83" t="s">
+        <v>653</v>
+      </c>
+      <c r="D83" t="s">
+        <v>315</v>
+      </c>
+      <c r="E83" t="s">
+        <v>285</v>
+      </c>
+      <c r="F83" t="s">
+        <v>654</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>656</v>
+      </c>
+      <c r="B84" t="s">
+        <v>657</v>
+      </c>
+      <c r="C84" t="s">
+        <v>303</v>
+      </c>
+      <c r="D84" t="s">
+        <v>315</v>
+      </c>
+      <c r="E84" t="s">
+        <v>658</v>
+      </c>
+      <c r="F84" t="s">
+        <v>421</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>660</v>
+      </c>
+      <c r="B85" t="s">
+        <v>661</v>
+      </c>
+      <c r="C85" t="s">
+        <v>303</v>
+      </c>
+      <c r="D85" t="s">
+        <v>315</v>
+      </c>
+      <c r="E85" t="s">
+        <v>662</v>
+      </c>
+      <c r="F85" t="s">
+        <v>663</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>665</v>
+      </c>
+      <c r="B86" t="s">
+        <v>666</v>
+      </c>
+      <c r="C86" t="s">
+        <v>667</v>
+      </c>
+      <c r="D86" t="s">
+        <v>315</v>
+      </c>
+      <c r="E86" t="s">
+        <v>449</v>
+      </c>
+      <c r="F86" t="s">
+        <v>668</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>670</v>
+      </c>
+      <c r="B87" t="s">
+        <v>605</v>
+      </c>
+      <c r="C87" t="s">
+        <v>303</v>
+      </c>
+      <c r="D87" t="s">
+        <v>291</v>
+      </c>
+      <c r="E87" t="s">
+        <v>671</v>
+      </c>
+      <c r="F87" t="s">
+        <v>530</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>673</v>
+      </c>
+      <c r="B88" t="s">
+        <v>674</v>
+      </c>
+      <c r="C88" t="s">
+        <v>309</v>
+      </c>
+      <c r="D88" t="s">
+        <v>315</v>
+      </c>
+      <c r="E88" t="s">
+        <v>675</v>
+      </c>
+      <c r="F88" t="s">
+        <v>676</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>678</v>
+      </c>
+      <c r="B89" t="s">
+        <v>679</v>
+      </c>
+      <c r="C89" t="s">
+        <v>680</v>
+      </c>
+      <c r="D89" t="s">
+        <v>315</v>
+      </c>
+      <c r="E89" t="s">
+        <v>681</v>
+      </c>
+      <c r="F89" t="s">
+        <v>682</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>684</v>
+      </c>
+      <c r="B90" t="s">
+        <v>685</v>
+      </c>
+      <c r="C90" t="s">
+        <v>686</v>
+      </c>
+      <c r="D90" t="s">
+        <v>315</v>
+      </c>
+      <c r="E90" t="s">
+        <v>687</v>
+      </c>
+      <c r="F90" t="s">
+        <v>349</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>684</v>
+      </c>
+      <c r="B91" t="s">
+        <v>552</v>
+      </c>
+      <c r="C91" t="s">
+        <v>303</v>
+      </c>
+      <c r="D91" t="s">
+        <v>315</v>
+      </c>
+      <c r="E91" t="s">
+        <v>689</v>
+      </c>
+      <c r="F91" t="s">
+        <v>421</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>691</v>
+      </c>
+      <c r="B92" t="s">
+        <v>346</v>
+      </c>
+      <c r="C92" t="s">
+        <v>692</v>
+      </c>
+      <c r="D92" t="s">
+        <v>315</v>
+      </c>
+      <c r="E92" t="s">
+        <v>619</v>
+      </c>
+      <c r="F92" t="s">
+        <v>349</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>694</v>
+      </c>
+      <c r="B93" t="s">
+        <v>552</v>
+      </c>
+      <c r="C93" t="s">
+        <v>303</v>
+      </c>
+      <c r="D93" t="s">
+        <v>315</v>
+      </c>
+      <c r="E93" t="s">
+        <v>695</v>
+      </c>
+      <c r="F93" t="s">
+        <v>421</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>697</v>
+      </c>
+      <c r="B94" t="s">
+        <v>698</v>
+      </c>
+      <c r="C94" t="s">
+        <v>493</v>
+      </c>
+      <c r="D94" t="s">
+        <v>315</v>
+      </c>
+      <c r="E94" t="s">
+        <v>699</v>
+      </c>
+      <c r="F94" t="s">
+        <v>285</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>701</v>
+      </c>
+      <c r="B95" t="s">
+        <v>702</v>
+      </c>
+      <c r="C95" t="s">
+        <v>303</v>
+      </c>
+      <c r="D95" t="s">
+        <v>315</v>
+      </c>
+      <c r="E95" t="s">
+        <v>703</v>
+      </c>
+      <c r="F95" t="s">
+        <v>704</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>706</v>
+      </c>
+      <c r="B96" t="s">
+        <v>707</v>
+      </c>
+      <c r="C96" t="s">
+        <v>708</v>
+      </c>
+      <c r="D96" t="s">
+        <v>315</v>
+      </c>
+      <c r="E96" t="s">
+        <v>709</v>
+      </c>
+      <c r="F96" t="s">
+        <v>710</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>712</v>
+      </c>
+      <c r="B97" t="s">
+        <v>335</v>
+      </c>
+      <c r="C97" t="s">
+        <v>303</v>
+      </c>
+      <c r="D97" t="s">
+        <v>315</v>
+      </c>
+      <c r="E97" t="s">
+        <v>713</v>
+      </c>
+      <c r="F97" t="s">
+        <v>337</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>715</v>
+      </c>
+      <c r="B98" t="s">
+        <v>335</v>
+      </c>
+      <c r="C98" t="s">
+        <v>303</v>
+      </c>
+      <c r="D98" t="s">
+        <v>315</v>
+      </c>
+      <c r="E98" t="s">
+        <v>713</v>
+      </c>
+      <c r="F98" t="s">
+        <v>337</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>717</v>
+      </c>
+      <c r="B99" t="s">
+        <v>718</v>
+      </c>
+      <c r="C99" t="s">
+        <v>719</v>
+      </c>
+      <c r="D99" t="s">
+        <v>398</v>
+      </c>
+      <c r="E99" t="s">
+        <v>285</v>
+      </c>
+      <c r="F99" t="s">
+        <v>720</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>717</v>
+      </c>
+      <c r="B100" t="s">
+        <v>718</v>
+      </c>
+      <c r="C100" t="s">
+        <v>719</v>
+      </c>
+      <c r="D100" t="s">
+        <v>398</v>
+      </c>
+      <c r="E100" t="s">
+        <v>285</v>
+      </c>
+      <c r="F100" t="s">
+        <v>720</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>723</v>
+      </c>
+      <c r="B101" t="s">
+        <v>724</v>
+      </c>
+      <c r="C101" t="s">
+        <v>309</v>
+      </c>
+      <c r="D101" t="s">
+        <v>315</v>
+      </c>
+      <c r="E101" t="s">
+        <v>725</v>
+      </c>
+      <c r="F101" t="s">
+        <v>726</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>728</v>
+      </c>
+      <c r="B102" t="s">
+        <v>413</v>
+      </c>
+      <c r="C102" t="s">
+        <v>290</v>
+      </c>
+      <c r="D102" t="s">
+        <v>315</v>
+      </c>
+      <c r="E102" t="s">
+        <v>729</v>
+      </c>
+      <c r="F102" t="s">
+        <v>415</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-02.xlsx
+++ b/docs/xlsx/jobs-2026-10-02.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="890">
   <si>
     <t>Title</t>
   </si>
@@ -880,6 +880,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/d4df8ed6a7a3475487538a2f00e413e9-lider-de-equipo-f2f-donantes-individuales-turno-manana-o-tarde-caba-ingenieria-sin-fronteras-argentina-buenos-aires</t>
   </si>
   <si>
+    <t>2026-27 African Dance Costume Assistant / Wardrobe</t>
+  </si>
+  <si>
+    <t>Saint Ann's School</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 3200.00 - 3400.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b613af31b9fd43d893de2d85fbcb8122-2026-27-african-dance-costume-assistant-wardrobe-saint-anns-school-kings-county</t>
+  </si>
+  <si>
+    <t>2026-27 Associate Costume Designer</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 2800.00 - 3200.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c6a24a24e21646039ba580ca66823d07-2026-27-associate-costume-designer-saint-anns-school-kings-county</t>
+  </si>
+  <si>
+    <t>2026-27 Certified Athletic Trainer - Per Diem</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4b98cd4353f54cb0ba9da6fd6e009dc6-2026-27-certified-athletic-trainer-per-diem-saint-anns-school-kings-county</t>
+  </si>
+  <si>
     <t>Academic Tutor</t>
   </si>
   <si>
@@ -937,6 +976,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/2d3ebb3e3f1a40d39c4fecce0b3bfe1e-adjunct-teacher-exalt-youth-new-york</t>
   </si>
   <si>
+    <t>Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Radnor Memorial Library</t>
+  </si>
+  <si>
+    <t>Wayne, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/69b8ddb2a19949f1b892883b6e3715cd-administrative-assistant-radnor-memorial-library-wayne</t>
+  </si>
+  <si>
     <t>ADMINISTRATIVE ASSISTANT - Washington State / State of Louisiana</t>
   </si>
   <si>
@@ -1084,6 +1141,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/f2dc0bbfea5a43a59e8feffd4ea716bc-bi-lingual-case-manager-coalition-for-the-homeless-new-york</t>
   </si>
   <si>
+    <t>Bilingual Administrative and Data Associate - Organizing Department</t>
+  </si>
+  <si>
+    <t>Community Organizing and Family Issues</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 48000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Children Youth, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fcc227390aea4b10aaf931c8b9540302-bilingual-administrative-and-data-associate-organizing-department-community-organizing-and-family-issues-chicago</t>
+  </si>
+  <si>
     <t>Bilingual Housing Counselor I</t>
   </si>
   <si>
@@ -1120,9 +1195,6 @@
     <t>Office Of the Community Liaison</t>
   </si>
   <si>
-    <t>Kings County, New York</t>
-  </si>
-  <si>
     <t>USD 68000.00 - 68000.00/year</t>
   </si>
   <si>
@@ -1132,6 +1204,21 @@
     <t>https://www.idealist.org/en/consultant-job/5178d6d2fd1f44d99460c36acfaeca63-bronx-community-organizer-office-of-the-community-liaison-kings-county</t>
   </si>
   <si>
+    <t>Building Manager</t>
+  </si>
+  <si>
+    <t>United Way of King County (WA State)</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 86896.00 - 91468.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0c7f5f1bc9684a34840c46f4f8d2e446-building-manager-united-way-of-king-county-wa-state-seattle</t>
+  </si>
+  <si>
     <t>Business &amp; Finance Manager</t>
   </si>
   <si>
@@ -1186,6 +1273,33 @@
     <t>https://www.idealist.org/en/consultant-job/cb9ca5e5b7dc4089a4692f67f9d587d6-chief-people-officer-rfk-community-alliance-eos-transition-partners-lancaster</t>
   </si>
   <si>
+    <t>Clean Energy Advocate</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 41750.00 - 46000.00/year</t>
+  </si>
+  <si>
+    <t>Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f00296442c0d4c92a15a13c595e52b1e-clean-energy-advocate-environment-america-oakland</t>
+  </si>
+  <si>
+    <t>Clean Water Advocate</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d68c08abd01241db9c6c2a9cef05ee92-clean-water-advocate-environment-america-boston</t>
+  </si>
+  <si>
     <t>Client Success Manager (Salesforce)</t>
   </si>
   <si>
@@ -1210,9 +1324,6 @@
     <t>Providence, RI</t>
   </si>
   <si>
-    <t>Part Time, Temporary</t>
-  </si>
-  <si>
     <t>USD 27000.00 - 27000.00/year</t>
   </si>
   <si>
@@ -1234,9 +1345,6 @@
     <t>USD 75000.00 - 85000.00/year</t>
   </si>
   <si>
-    <t>Environment</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/545546f9bc474c08bc737461786aeec4-communications-manager-elkhorn-slough-foundation-watsonville</t>
   </si>
   <si>
@@ -1267,6 +1375,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/2146f56cbc2e4edf907e03d8a73d8861-community-advocate-housing-rights-program-asian-law-caucus-san-francisco</t>
   </si>
   <si>
+    <t>Company Manager</t>
+  </si>
+  <si>
+    <t>The Washington Ballet</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4b680b40e0874260b94791791e6c93dd-company-manager-the-washington-ballet-washington</t>
+  </si>
+  <si>
     <t>CONSUMER STAFF ATTORNEY – BROCKTON LAW OFFICE</t>
   </si>
   <si>
@@ -1285,21 +1408,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/1a2a1b6775b343c29f24855d0966aed2-consumer-staff-attorney-brockton-law-office-south-coastal-counties-legal-services-inc-brockton</t>
   </si>
   <si>
+    <t>Content and Communications Specialist</t>
+  </si>
+  <si>
+    <t>Partnership for Civil Justice</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c84376ef1e544d1bb092654314a08c3d-content-and-communications-specialist-partnership-for-civil-justice-washington</t>
+  </si>
+  <si>
+    <t>Coordinador@ de Desarrollo Económico</t>
+  </si>
+  <si>
+    <t>Fundación Genera</t>
+  </si>
+  <si>
+    <t>Cancún, Quintana Roo, MX</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ffc7618992644718d3c23315bda8e7e-coordinador-de-desarrollo-economico-fundacion-genera-cancun</t>
+  </si>
+  <si>
     <t>Coordinator, Programs</t>
   </si>
   <si>
     <t>LINK Unlimited Scholars</t>
   </si>
   <si>
-    <t>Chicago, Illinois</t>
-  </si>
-  <si>
     <t>USD 48000.00 - 53000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/b8c41acbc9c74f3c82fb049e83294ef3-coordinator-programs-link-unlimited-scholars-chicago</t>
   </si>
   <si>
@@ -1315,6 +1459,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/251c21e682f24734945c67e0cc0d3b4e-corporate-partnerships-associate-rescuing-leftover-cuisine-new-york</t>
   </si>
   <si>
+    <t>Criminal/Immigration Senior Staff or Managing Attorneys</t>
+  </si>
+  <si>
+    <t>Immigrant Legal Resource Center</t>
+  </si>
+  <si>
+    <t>USD 112492.23/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8c0795680d3f4e9396ffdbde986cfbe5-criminalimmigration-senior-staff-or-managing-attorneys-immigrant-legal-resource-center-san-francisco</t>
+  </si>
+  <si>
+    <t>Remote (Fresno, California)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2bb17d45ab0542ec97ecb15828bd74ff-criminalimmigration-senior-staff-or-managing-attorneys-immigrant-legal-resource-center-fresno</t>
+  </si>
+  <si>
+    <t>Remote (Los Angeles, California)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5305c8708caa4031a42331c71f694b94-criminalimmigration-senior-staff-or-managing-attorneys-immigrant-legal-resource-center-los-angeles</t>
+  </si>
+  <si>
     <t>CRM Coordinator &amp; Systems Support</t>
   </si>
   <si>
@@ -1372,6 +1543,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/82eb4fe88c4c4200bda850f2cc5376e5-development-coordinator-childrens-learning-centers-of-fairfield-county-stamford</t>
   </si>
   <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Tree House Books</t>
+  </si>
+  <si>
+    <t>Philadelphia, PA</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b8c2623897d46e8ae1d9ea1168b7c15-development-director-tree-house-books-philadelphia</t>
+  </si>
+  <si>
+    <t>Vineyard Conservation Society</t>
+  </si>
+  <si>
+    <t>Tisbury, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ee17b18a669240a9bdf9122eca2aacda-development-director-vineyard-conservation-society-tisbury</t>
+  </si>
+  <si>
     <t>Director of Communications</t>
   </si>
   <si>
@@ -1402,6 +1606,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/d2a3bbf769bc416ea6b47545cbfc31b8-director-of-development-brooklyn-boatworks-new-york</t>
   </si>
   <si>
+    <t>Director of Development &amp; Enrollment</t>
+  </si>
+  <si>
+    <t>Tennessee Health Care Campaign</t>
+  </si>
+  <si>
+    <t>Remote (Tennessee)</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4f5db4a6d521491faa14e639fc9c8271-director-of-development-enrollment-tennessee-health-care-campaign-nashville</t>
+  </si>
+  <si>
     <t>Director of Finance and Administration</t>
   </si>
   <si>
@@ -1420,6 +1642,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/8dcd495d865149ef9ff163e450cc0f58-director-of-finance-and-administration-sadie-nash-leadership-project-new-york</t>
   </si>
   <si>
+    <t>Director of Finance and Business Operations</t>
+  </si>
+  <si>
+    <t>Ecumenical Ministries of Oregon</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 91000.00 - 96000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Housing Homelessness, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b95548cf22d54f7689cd34b8ed285344-director-of-finance-and-business-operations-ecumenical-ministries-of-oregon-portland</t>
+  </si>
+  <si>
+    <t>Director of Human Resources</t>
+  </si>
+  <si>
+    <t>Lambda Legal</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/542476df0f644cb19b22f38dcee29d89-director-of-human-resources-lambda-legal-new-york</t>
+  </si>
+  <si>
     <t>Director of Operations</t>
   </si>
   <si>
@@ -1495,9 +1747,6 @@
     <t>Supported Solution</t>
   </si>
   <si>
-    <t>Seattle, Washington</t>
-  </si>
-  <si>
     <t>USD 23.00 - 25.00/hour</t>
   </si>
   <si>
@@ -1507,6 +1756,36 @@
     <t>https://www.idealist.org/en/business-job/defe6b21dbca42669e85e0f730dee114-employment-consultant-supported-solution-seattle</t>
   </si>
   <si>
+    <t>Employment Retention Specialist</t>
+  </si>
+  <si>
+    <t>Project Place</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>USD 49000.00 - 51000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a2a351b071174fa8a8cce415c120ac06-employment-retention-specialist-project-place-boston</t>
+  </si>
+  <si>
+    <t>End Food Waste Campaign Associate</t>
+  </si>
+  <si>
+    <t>U.S. PIRG</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2baa758a00bc40b5afa6969df48307b3-end-food-waste-campaign-associate-us-pirg-portland</t>
+  </si>
+  <si>
     <t>Environmental Campaigner</t>
   </si>
   <si>
@@ -1570,6 +1849,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/10e61b4e8822496ab2b1646b97926e21-environmental-campaigner-green-corps-pittsburgh</t>
   </si>
   <si>
+    <t>Environmental State Director, Wyoming</t>
+  </si>
+  <si>
+    <t>Cheyenne, Wyoming</t>
+  </si>
+  <si>
+    <t>USD 43000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d301c5a6a65b4243b50a1133a9cbaa3d-environmental-state-director-wyoming-environment-america-cheyenne</t>
+  </si>
+  <si>
     <t>Executive Assistant - Recovery Services Bureau</t>
   </si>
   <si>
@@ -1588,9 +1879,6 @@
     <t>USD 205000.00 - 240000.00/year</t>
   </si>
   <si>
-    <t>Health Medicine</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/bbdbab21317f4f6ca3c1e68a5929a15f-executive-director-alliance-for-innovation-in-global-health-san-francisco</t>
   </si>
   <si>
@@ -1606,9 +1894,6 @@
     <t>USD 120000.00 - 125000.00/year</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/consultant-job/fb5a59b8aa564d3e84699c215d4e851f-executive-director-muddy-sneakers-armstrong-mcguire-associates-raleigh</t>
   </si>
   <si>
@@ -1645,9 +1930,6 @@
     <t>The Drama League</t>
   </si>
   <si>
-    <t>USD 70000.00 - 70000.00/year</t>
-  </si>
-  <si>
     <t>Arts Music, Education, Media</t>
   </si>
   <si>
@@ -1681,6 +1963,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/ed1f6dd6e02243e48079995bf0dbe2be-finance-coordinator-new-york-legal-assistance-group-nylag-new-york</t>
   </si>
   <si>
+    <t>Finance Operations Specialist</t>
+  </si>
+  <si>
+    <t>Protect Democracy</t>
+  </si>
+  <si>
+    <t>USD 84300.00 - 94000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/320d8a58a6e84bf6bbfd1805b5e52d66-finance-operations-specialist-protect-democracy-washington</t>
+  </si>
+  <si>
+    <t>Grants Manager</t>
+  </si>
+  <si>
+    <t>Big Brothers Big Sisters Columbia Northwest</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/bd7e9dc9ba304f7f86a80b3cb02f62a9-grants-manager-big-brothers-big-sisters-columbia-northwest-portland</t>
+  </si>
+  <si>
     <t>Graphic Designer</t>
   </si>
   <si>
@@ -1699,6 +2005,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/a49af641ec9042a5bfa3af5aa4cbc5aa-graphic-designer-us-center-for-safesport-denver</t>
   </si>
   <si>
+    <t>Health Care Advocate</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Transparency Oversight, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/95e3b2719fef442da3d5b2bbefe38cfa-health-care-advocate-us-pirg-portland</t>
+  </si>
+  <si>
     <t>Housing Supervising Attorney</t>
   </si>
   <si>
@@ -1765,6 +2080,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/c5aaaff46ac44a5ba3b906ad51fedd02-legal-data-grants-compliance-manager-asian-law-caucus-san-francisco</t>
   </si>
   <si>
+    <t>Make Textbooks Affordable Campaign Organizer</t>
+  </si>
+  <si>
+    <t>Student PIRGs</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Consumer Protection</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f3d7c2d6dcfd4147a78a90a5b2a07885-make-textbooks-affordable-campaign-organizer-student-pirgs-boston</t>
+  </si>
+  <si>
+    <t>New Brunswick, New Jersey</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d70e6eeb3b9f4faf99863f04066f2cc4-make-textbooks-affordable-campaign-organizer-student-pirgs-new-brunswick</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/01d62caab5e746fa922cdd90b2ccbe0e-make-textbooks-affordable-campaign-organizer-student-pirgs-washington</t>
+  </si>
+  <si>
     <t>Managing Director - Hadassah Mid Atlantic</t>
   </si>
   <si>
@@ -1888,6 +2224,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/9b8e2c3f55d848339241772b91f83785-ovs-office-of-victim-services-staff-attorney-peekskill-legal-services-of-the-hudson-valley-peekskill</t>
   </si>
   <si>
+    <t>Paralegal &amp; Litigation Specialist</t>
+  </si>
+  <si>
+    <t>USD 84300.00 - 99200.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/da0715726d5d4fad80d67dc11df56b07-paralegal-litigation-specialist-protect-democracy-washington</t>
+  </si>
+  <si>
     <t>Parish Secretary</t>
   </si>
   <si>
@@ -1924,9 +2269,6 @@
     <t>American Association of State Highway &amp; Transportation Officials</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 80000.00 - 110000.00/year</t>
   </si>
   <si>
@@ -1954,6 +2296,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/2f96cd5232e24b91be6797a14b656596-program-officer-outreach-and-education-chesapeake-bay-trust-annapolis</t>
   </si>
   <si>
+    <t>Progressive Talent Pipeline Endorsement</t>
+  </si>
+  <si>
+    <t>Progressive Talent Pipeline</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4102c94f7a224aad9855665a90283005-progressive-talent-pipeline-endorsement-progressive-talent-pipeline-washington</t>
+  </si>
+  <si>
     <t>Project Coordinator</t>
   </si>
   <si>
@@ -2035,6 +2386,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/75fc7e73e44144b0be910ae864502d29-resource-navigator-part-time-cancer-care-inc-new-york</t>
   </si>
   <si>
+    <t>Senior Loan Officer</t>
+  </si>
+  <si>
+    <t>The Housing Partnership Network</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aa8a19698cf5438aa15a6480ea47826e-senior-loan-officer-the-housing-partnership-network-boston</t>
+  </si>
+  <si>
     <t>Senior Manager of Digital Marketing</t>
   </si>
   <si>
@@ -2050,6 +2416,57 @@
     <t>https://www.idealist.org/en/nonprofit-job/fb8c0747fce847f5b8e0f1181c852cbb-senior-manager-of-digital-marketing-keep-america-beautiful-inc-stamford</t>
   </si>
   <si>
+    <t>Senior Probate Attorney</t>
+  </si>
+  <si>
+    <t>Open Door Legal</t>
+  </si>
+  <si>
+    <t>USD 89500.00 - 111500.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7aef6f86ab6e46fb9b4af525880ce52c-senior-probate-attorney-open-door-legal-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Specialist, Membership</t>
+  </si>
+  <si>
+    <t>National Geographic Society</t>
+  </si>
+  <si>
+    <t>USD 71250.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Philanthropy, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/725e697e96d14d57bb4f43776ab6e5d2-senior-specialist-membership-national-geographic-society-washington</t>
+  </si>
+  <si>
+    <t>Senior Staff Attorney</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b683be1114b345e2aa0ee8fa0a6b16a5-senior-staff-attorney-immigrant-legal-resource-center-san-francisco</t>
+  </si>
+  <si>
+    <t>Site Supervision Manager</t>
+  </si>
+  <si>
+    <t>YouthPlaces</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0f4d6ae04e544306b73c40fa290acba8-site-supervision-manager-youthplaces-pittsburgh</t>
+  </si>
+  <si>
     <t>Special Assistant to the Executive Director &amp; COO</t>
   </si>
   <si>
@@ -2098,6 +2515,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/86e15ed6616e4f14bd85840f19477665-staff-attorney-domestic-violencegeneral-practice-legal-services-of-the-hudson-valley-goshen</t>
   </si>
   <si>
+    <t>Staff Attorney - Housing Justice</t>
+  </si>
+  <si>
+    <t>SeniorLAW Center</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 66000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Housing Homelessness, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/911a1074059145548969fe3edaf947c7-staff-attorney-housing-justice-seniorlaw-center-philadelphia</t>
+  </si>
+  <si>
     <t>Staff Attorney / Health Advocacy Fellow (2-year position)</t>
   </si>
   <si>
@@ -2107,6 +2542,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/1f31ec5134954e998af0b06379325345-staff-attorney-health-advocacy-fellow-2-year-position-new-york-legal-assistance-group-nylag-new-york</t>
   </si>
   <si>
+    <t>Supervising Attorney, Immigration</t>
+  </si>
+  <si>
+    <t>UFW Foundation</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/40af425d642b4bf58c6e1a1800a9d7ff-supervising-attorney-immigration-ufw-foundation-bakersfield</t>
+  </si>
+  <si>
+    <t>Supervising Attorney, Workers’ Rights</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3888004aa5b749209924ff9e4669e8a8-supervising-attorney-workers-rights-ufw-foundation-bakersfield</t>
+  </si>
+  <si>
     <t>Systems &amp; Operations Coordinator</t>
   </si>
   <si>
@@ -2119,6 +2581,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/7bd9a20500924ec8977ee2d525d581ed-systems-operations-coordinator-panorama-global-seattle</t>
   </si>
   <si>
+    <t>Tax Site Manager (Temporary)</t>
+  </si>
+  <si>
+    <t>USD 27.68 - 27.68/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f8c337f0198f486bbc62f2754f62b9d0-tax-site-manager-temporary-united-way-of-king-county-wa-state-seattle</t>
+  </si>
+  <si>
+    <t>Temporary Probate Attorney</t>
+  </si>
+  <si>
+    <t>USD 40.14 - 47.84/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/75633856f6e64782b4bbf8b57111b4da-temporary-probate-attorney-open-door-legal-san-francisco</t>
+  </si>
+  <si>
     <t>Tenant Organizer (Bilingual Spanish/English)</t>
   </si>
   <si>
@@ -2138,9 +2618,6 @@
   </si>
   <si>
     <t>People Power (Talent Agency)</t>
-  </si>
-  <si>
-    <t>Oakland, California</t>
   </si>
   <si>
     <t>USD 115000.00 - 115000.00/year</t>
@@ -4058,7 +4535,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H142"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -4131,2293 +4608,3213 @@
         <v>290</v>
       </c>
       <c r="D3" t="s">
+        <v>284</v>
+      </c>
+      <c r="E3" t="s">
         <v>291</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>292</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C4" t="s">
+        <v>290</v>
+      </c>
+      <c r="D4" t="s">
         <v>295</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E4" t="s">
         <v>296</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>297</v>
       </c>
-      <c r="D4" t="s">
-        <v>291</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="H4" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="F4" t="s">
-        <v>299</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B5" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="C5" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="D5" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="E5" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="F5" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C6" t="s">
+        <v>303</v>
+      </c>
+      <c r="D6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E6" t="s">
+        <v>305</v>
+      </c>
+      <c r="F6" t="s">
+        <v>306</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="B6" t="s">
-        <v>308</v>
-      </c>
-      <c r="C6" t="s">
-        <v>309</v>
-      </c>
-      <c r="D6" t="s">
-        <v>291</v>
-      </c>
-      <c r="E6" t="s">
-        <v>310</v>
-      </c>
-      <c r="F6" t="s">
-        <v>311</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>308</v>
+      </c>
+      <c r="B7" t="s">
+        <v>309</v>
+      </c>
+      <c r="C7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D7" t="s">
+        <v>304</v>
+      </c>
+      <c r="E7" t="s">
+        <v>311</v>
+      </c>
+      <c r="F7" t="s">
+        <v>312</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="B7" t="s">
-        <v>314</v>
-      </c>
-      <c r="C7" t="s">
-        <v>303</v>
-      </c>
-      <c r="D7" t="s">
-        <v>315</v>
-      </c>
-      <c r="E7" t="s">
-        <v>316</v>
-      </c>
-      <c r="F7" t="s">
-        <v>317</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>314</v>
+      </c>
+      <c r="B8" t="s">
+        <v>315</v>
+      </c>
+      <c r="C8" t="s">
+        <v>316</v>
+      </c>
+      <c r="D8" t="s">
+        <v>304</v>
+      </c>
+      <c r="E8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F8" t="s">
+        <v>318</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="B8" t="s">
-        <v>320</v>
-      </c>
-      <c r="C8" t="s">
-        <v>321</v>
-      </c>
-      <c r="D8" t="s">
-        <v>284</v>
-      </c>
-      <c r="E8" t="s">
-        <v>322</v>
-      </c>
-      <c r="F8" t="s">
-        <v>323</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>320</v>
+      </c>
+      <c r="B9" t="s">
+        <v>321</v>
+      </c>
+      <c r="C9" t="s">
+        <v>322</v>
+      </c>
+      <c r="D9" t="s">
+        <v>304</v>
+      </c>
+      <c r="E9" t="s">
+        <v>323</v>
+      </c>
+      <c r="F9" t="s">
+        <v>324</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="B9" t="s">
-        <v>320</v>
-      </c>
-      <c r="C9" t="s">
-        <v>321</v>
-      </c>
-      <c r="D9" t="s">
-        <v>284</v>
-      </c>
-      <c r="E9" t="s">
-        <v>322</v>
-      </c>
-      <c r="F9" t="s">
-        <v>323</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>326</v>
+      </c>
+      <c r="B10" t="s">
         <v>327</v>
       </c>
-      <c r="B10" t="s">
-        <v>320</v>
-      </c>
       <c r="C10" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="D10" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="E10" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="F10" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B11" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C11" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="D11" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E11" t="s">
-        <v>285</v>
+        <v>335</v>
       </c>
       <c r="F11" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B12" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C12" t="s">
-        <v>303</v>
+        <v>340</v>
       </c>
       <c r="D12" t="s">
-        <v>315</v>
+        <v>284</v>
       </c>
       <c r="E12" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F12" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>344</v>
+      </c>
+      <c r="B13" t="s">
         <v>339</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>340</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>284</v>
+      </c>
+      <c r="E13" t="s">
         <v>341</v>
       </c>
-      <c r="D13" t="s">
-        <v>315</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>342</v>
       </c>
-      <c r="F13" t="s">
-        <v>343</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B14" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C14" t="s">
+        <v>340</v>
+      </c>
+      <c r="D14" t="s">
+        <v>284</v>
+      </c>
+      <c r="E14" t="s">
+        <v>341</v>
+      </c>
+      <c r="F14" t="s">
+        <v>342</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="D14" t="s">
-        <v>315</v>
-      </c>
-      <c r="E14" t="s">
-        <v>348</v>
-      </c>
-      <c r="F14" t="s">
-        <v>349</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>348</v>
+      </c>
+      <c r="B15" t="s">
+        <v>349</v>
+      </c>
+      <c r="C15" t="s">
+        <v>350</v>
+      </c>
+      <c r="D15" t="s">
+        <v>334</v>
+      </c>
+      <c r="E15" t="s">
+        <v>285</v>
+      </c>
+      <c r="F15" t="s">
         <v>351</v>
       </c>
-      <c r="B15" t="s">
+      <c r="H15" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="C15" t="s">
-        <v>303</v>
-      </c>
-      <c r="D15" t="s">
-        <v>315</v>
-      </c>
-      <c r="E15" t="s">
-        <v>353</v>
-      </c>
-      <c r="F15" t="s">
-        <v>354</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>353</v>
+      </c>
+      <c r="B16" t="s">
+        <v>354</v>
+      </c>
+      <c r="C16" t="s">
+        <v>316</v>
+      </c>
+      <c r="D16" t="s">
+        <v>334</v>
+      </c>
+      <c r="E16" t="s">
+        <v>355</v>
+      </c>
+      <c r="F16" t="s">
         <v>356</v>
       </c>
-      <c r="B16" t="s">
+      <c r="H16" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="C16" t="s">
-        <v>358</v>
-      </c>
-      <c r="D16" t="s">
-        <v>315</v>
-      </c>
-      <c r="E16" t="s">
-        <v>359</v>
-      </c>
-      <c r="F16" t="s">
-        <v>360</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>358</v>
+      </c>
+      <c r="B17" t="s">
+        <v>359</v>
+      </c>
+      <c r="C17" t="s">
+        <v>360</v>
+      </c>
+      <c r="D17" t="s">
+        <v>334</v>
+      </c>
+      <c r="E17" t="s">
+        <v>361</v>
+      </c>
+      <c r="F17" t="s">
         <v>362</v>
       </c>
-      <c r="B17" t="s">
+      <c r="H17" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="C17" t="s">
-        <v>309</v>
-      </c>
-      <c r="D17" t="s">
-        <v>291</v>
-      </c>
-      <c r="E17" t="s">
-        <v>285</v>
-      </c>
-      <c r="F17" t="s">
-        <v>364</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>364</v>
+      </c>
+      <c r="B18" t="s">
+        <v>365</v>
+      </c>
+      <c r="C18" t="s">
         <v>366</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
+        <v>334</v>
+      </c>
+      <c r="E18" t="s">
         <v>367</v>
       </c>
-      <c r="C18" t="s">
+      <c r="F18" t="s">
         <v>368</v>
       </c>
-      <c r="D18" t="s">
-        <v>315</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="H18" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="F18" t="s">
-        <v>370</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>370</v>
+      </c>
+      <c r="B19" t="s">
+        <v>371</v>
+      </c>
+      <c r="C19" t="s">
+        <v>316</v>
+      </c>
+      <c r="D19" t="s">
+        <v>334</v>
+      </c>
+      <c r="E19" t="s">
         <v>372</v>
       </c>
-      <c r="B19" t="s">
+      <c r="F19" t="s">
         <v>373</v>
       </c>
-      <c r="C19" t="s">
+      <c r="H19" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="D19" t="s">
-        <v>291</v>
-      </c>
-      <c r="E19" t="s">
-        <v>375</v>
-      </c>
-      <c r="F19" t="s">
-        <v>376</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>375</v>
+      </c>
+      <c r="B20" t="s">
+        <v>376</v>
+      </c>
+      <c r="C20" t="s">
+        <v>377</v>
+      </c>
+      <c r="D20" t="s">
+        <v>334</v>
+      </c>
+      <c r="E20" t="s">
         <v>378</v>
       </c>
-      <c r="B20" t="s">
+      <c r="F20" t="s">
         <v>379</v>
       </c>
-      <c r="C20" t="s">
+      <c r="H20" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="D20" t="s">
-        <v>315</v>
-      </c>
-      <c r="E20" t="s">
-        <v>381</v>
-      </c>
-      <c r="F20" t="s">
-        <v>382</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>381</v>
+      </c>
+      <c r="B21" t="s">
+        <v>382</v>
+      </c>
+      <c r="C21" t="s">
+        <v>383</v>
+      </c>
+      <c r="D21" t="s">
+        <v>334</v>
+      </c>
+      <c r="E21" t="s">
         <v>384</v>
       </c>
-      <c r="B21" t="s">
+      <c r="F21" t="s">
         <v>385</v>
       </c>
-      <c r="C21" t="s">
+      <c r="H21" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="D21" t="s">
-        <v>315</v>
-      </c>
-      <c r="E21" t="s">
-        <v>387</v>
-      </c>
-      <c r="F21" t="s">
-        <v>388</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>387</v>
+      </c>
+      <c r="B22" t="s">
+        <v>388</v>
+      </c>
+      <c r="C22" t="s">
+        <v>328</v>
+      </c>
+      <c r="D22" t="s">
+        <v>304</v>
+      </c>
+      <c r="E22" t="s">
+        <v>285</v>
+      </c>
+      <c r="F22" t="s">
+        <v>389</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="B22" t="s">
-        <v>391</v>
-      </c>
-      <c r="C22" t="s">
-        <v>309</v>
-      </c>
-      <c r="D22" t="s">
-        <v>315</v>
-      </c>
-      <c r="E22" t="s">
-        <v>392</v>
-      </c>
-      <c r="F22" t="s">
-        <v>393</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>391</v>
+      </c>
+      <c r="B23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C23" t="s">
+        <v>290</v>
+      </c>
+      <c r="D23" t="s">
+        <v>334</v>
+      </c>
+      <c r="E23" t="s">
+        <v>393</v>
+      </c>
+      <c r="F23" t="s">
+        <v>394</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="B23" t="s">
-        <v>396</v>
-      </c>
-      <c r="C23" t="s">
-        <v>397</v>
-      </c>
-      <c r="D23" t="s">
-        <v>398</v>
-      </c>
-      <c r="E23" t="s">
-        <v>399</v>
-      </c>
-      <c r="F23" t="s">
-        <v>400</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="B24" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C24" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="D24" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E24" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="F24" t="s">
-        <v>406</v>
+        <v>285</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>401</v>
+      </c>
+      <c r="B25" t="s">
         <v>402</v>
       </c>
-      <c r="B25" t="s">
-        <v>408</v>
-      </c>
       <c r="C25" t="s">
-        <v>303</v>
+        <v>403</v>
       </c>
       <c r="D25" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="E25" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="F25" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>407</v>
+      </c>
+      <c r="B26" t="s">
+        <v>408</v>
+      </c>
+      <c r="C26" t="s">
+        <v>409</v>
+      </c>
+      <c r="D26" t="s">
+        <v>334</v>
+      </c>
+      <c r="E26" t="s">
+        <v>410</v>
+      </c>
+      <c r="F26" t="s">
+        <v>411</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="B26" t="s">
-        <v>413</v>
-      </c>
-      <c r="C26" t="s">
-        <v>290</v>
-      </c>
-      <c r="D26" t="s">
-        <v>315</v>
-      </c>
-      <c r="E26" t="s">
-        <v>414</v>
-      </c>
-      <c r="F26" t="s">
-        <v>415</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>413</v>
+      </c>
+      <c r="B27" t="s">
+        <v>414</v>
+      </c>
+      <c r="C27" t="s">
+        <v>415</v>
+      </c>
+      <c r="D27" t="s">
+        <v>334</v>
+      </c>
+      <c r="E27" t="s">
+        <v>416</v>
+      </c>
+      <c r="F27" t="s">
         <v>417</v>
       </c>
-      <c r="B27" t="s">
+      <c r="H27" s="2" t="s">
         <v>418</v>
-      </c>
-      <c r="C27" t="s">
-        <v>419</v>
-      </c>
-      <c r="D27" t="s">
-        <v>315</v>
-      </c>
-      <c r="E27" t="s">
-        <v>420</v>
-      </c>
-      <c r="F27" t="s">
-        <v>421</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>419</v>
+      </c>
+      <c r="B28" t="s">
+        <v>420</v>
+      </c>
+      <c r="C28" t="s">
+        <v>421</v>
+      </c>
+      <c r="D28" t="s">
+        <v>334</v>
+      </c>
+      <c r="E28" t="s">
+        <v>422</v>
+      </c>
+      <c r="F28" t="s">
         <v>423</v>
       </c>
-      <c r="B28" t="s">
+      <c r="H28" s="2" t="s">
         <v>424</v>
-      </c>
-      <c r="C28" t="s">
-        <v>425</v>
-      </c>
-      <c r="D28" t="s">
-        <v>315</v>
-      </c>
-      <c r="E28" t="s">
-        <v>426</v>
-      </c>
-      <c r="F28" t="s">
-        <v>427</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B29" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C29" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="D29" t="s">
-        <v>284</v>
+        <v>334</v>
       </c>
       <c r="E29" t="s">
-        <v>322</v>
+        <v>422</v>
       </c>
       <c r="F29" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B30" t="s">
-        <v>285</v>
+        <v>429</v>
       </c>
       <c r="C30" t="s">
-        <v>434</v>
+        <v>328</v>
       </c>
       <c r="D30" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E30" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F30" t="s">
-        <v>285</v>
+        <v>431</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>433</v>
+      </c>
+      <c r="B31" t="s">
+        <v>434</v>
+      </c>
+      <c r="C31" t="s">
+        <v>435</v>
+      </c>
+      <c r="D31" t="s">
+        <v>295</v>
+      </c>
+      <c r="E31" t="s">
+        <v>436</v>
+      </c>
+      <c r="F31" t="s">
         <v>437</v>
       </c>
-      <c r="B31" t="s">
+      <c r="H31" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="C31" t="s">
-        <v>207</v>
-      </c>
-      <c r="D31" t="s">
-        <v>315</v>
-      </c>
-      <c r="E31" t="s">
-        <v>439</v>
-      </c>
-      <c r="F31" t="s">
-        <v>440</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>439</v>
+      </c>
+      <c r="B32" t="s">
+        <v>440</v>
+      </c>
+      <c r="C32" t="s">
+        <v>441</v>
+      </c>
+      <c r="D32" t="s">
+        <v>334</v>
+      </c>
+      <c r="E32" t="s">
         <v>442</v>
       </c>
-      <c r="B32" t="s">
+      <c r="F32" t="s">
+        <v>426</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>443</v>
-      </c>
-      <c r="C32" t="s">
-        <v>425</v>
-      </c>
-      <c r="D32" t="s">
-        <v>315</v>
-      </c>
-      <c r="E32" t="s">
-        <v>353</v>
-      </c>
-      <c r="F32" t="s">
-        <v>444</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>439</v>
+      </c>
+      <c r="B33" t="s">
+        <v>444</v>
+      </c>
+      <c r="C33" t="s">
+        <v>316</v>
+      </c>
+      <c r="D33" t="s">
+        <v>334</v>
+      </c>
+      <c r="E33" t="s">
+        <v>445</v>
+      </c>
+      <c r="F33" t="s">
         <v>446</v>
       </c>
-      <c r="B33" t="s">
+      <c r="H33" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="C33" t="s">
-        <v>448</v>
-      </c>
-      <c r="D33" t="s">
-        <v>315</v>
-      </c>
-      <c r="E33" t="s">
-        <v>449</v>
-      </c>
-      <c r="F33" t="s">
-        <v>450</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>448</v>
+      </c>
+      <c r="B34" t="s">
+        <v>449</v>
+      </c>
+      <c r="C34" t="s">
+        <v>303</v>
+      </c>
+      <c r="D34" t="s">
+        <v>334</v>
+      </c>
+      <c r="E34" t="s">
+        <v>450</v>
+      </c>
+      <c r="F34" t="s">
+        <v>451</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="B34" t="s">
-        <v>453</v>
-      </c>
-      <c r="C34" t="s">
-        <v>309</v>
-      </c>
-      <c r="D34" t="s">
-        <v>315</v>
-      </c>
-      <c r="E34" t="s">
-        <v>454</v>
-      </c>
-      <c r="F34" t="s">
-        <v>455</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>453</v>
+      </c>
+      <c r="B35" t="s">
+        <v>454</v>
+      </c>
+      <c r="C35" t="s">
+        <v>455</v>
+      </c>
+      <c r="D35" t="s">
+        <v>334</v>
+      </c>
+      <c r="E35" t="s">
+        <v>456</v>
+      </c>
+      <c r="F35" t="s">
+        <v>285</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="B35" t="s">
-        <v>458</v>
-      </c>
-      <c r="C35" t="s">
-        <v>303</v>
-      </c>
-      <c r="D35" t="s">
-        <v>315</v>
-      </c>
-      <c r="E35" t="s">
-        <v>459</v>
-      </c>
-      <c r="F35" t="s">
-        <v>460</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>458</v>
+      </c>
+      <c r="B36" t="s">
+        <v>459</v>
+      </c>
+      <c r="C36" t="s">
+        <v>460</v>
+      </c>
+      <c r="D36" t="s">
+        <v>334</v>
+      </c>
+      <c r="E36" t="s">
+        <v>461</v>
+      </c>
+      <c r="F36" t="s">
         <v>462</v>
       </c>
-      <c r="B36" t="s">
+      <c r="H36" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="C36" t="s">
-        <v>464</v>
-      </c>
-      <c r="D36" t="s">
-        <v>315</v>
-      </c>
-      <c r="E36" t="s">
-        <v>336</v>
-      </c>
-      <c r="F36" t="s">
-        <v>465</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B37" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C37" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="D37" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E37" t="s">
-        <v>336</v>
+        <v>466</v>
       </c>
       <c r="F37" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B38" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C38" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D38" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E38" t="s">
-        <v>471</v>
+        <v>285</v>
       </c>
       <c r="F38" t="s">
+        <v>437</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B39" t="s">
         <v>474</v>
       </c>
       <c r="C39" t="s">
+        <v>377</v>
+      </c>
+      <c r="D39" t="s">
+        <v>334</v>
+      </c>
+      <c r="E39" t="s">
         <v>475</v>
       </c>
-      <c r="D39" t="s">
-        <v>315</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
+        <v>292</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="F39" t="s">
-        <v>477</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>477</v>
+      </c>
+      <c r="B40" t="s">
+        <v>478</v>
+      </c>
+      <c r="C40" t="s">
+        <v>316</v>
+      </c>
+      <c r="D40" t="s">
+        <v>284</v>
+      </c>
+      <c r="E40" t="s">
+        <v>341</v>
+      </c>
+      <c r="F40" t="s">
         <v>479</v>
       </c>
-      <c r="B40" t="s">
-        <v>346</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="H40" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="D40" t="s">
-        <v>315</v>
-      </c>
-      <c r="E40" t="s">
-        <v>481</v>
-      </c>
-      <c r="F40" t="s">
-        <v>349</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>481</v>
+      </c>
+      <c r="B41" t="s">
+        <v>482</v>
+      </c>
+      <c r="C41" t="s">
+        <v>303</v>
+      </c>
+      <c r="D41" t="s">
+        <v>334</v>
+      </c>
+      <c r="E41" t="s">
         <v>483</v>
       </c>
-      <c r="B41" t="s">
+      <c r="F41" t="s">
         <v>484</v>
       </c>
-      <c r="C41" t="s">
-        <v>309</v>
-      </c>
-      <c r="D41" t="s">
-        <v>284</v>
-      </c>
-      <c r="E41" t="s">
-        <v>285</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="H41" s="2" t="s">
         <v>485</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>481</v>
+      </c>
+      <c r="B42" t="s">
+        <v>482</v>
+      </c>
+      <c r="C42" t="s">
+        <v>486</v>
+      </c>
+      <c r="D42" t="s">
+        <v>334</v>
+      </c>
+      <c r="E42" t="s">
+        <v>483</v>
+      </c>
+      <c r="F42" t="s">
+        <v>484</v>
+      </c>
+      <c r="H42" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="B42" t="s">
-        <v>488</v>
-      </c>
-      <c r="C42" t="s">
-        <v>368</v>
-      </c>
-      <c r="D42" t="s">
-        <v>315</v>
-      </c>
-      <c r="E42" t="s">
-        <v>489</v>
-      </c>
-      <c r="F42" t="s">
-        <v>285</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="B43" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="C43" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="D43" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E43" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="F43" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="B44" t="s">
-        <v>498</v>
+        <v>285</v>
       </c>
       <c r="C44" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="D44" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E44" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="F44" t="s">
-        <v>501</v>
+        <v>285</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>494</v>
+      </c>
+      <c r="B45" t="s">
+        <v>495</v>
+      </c>
+      <c r="C45" t="s">
+        <v>207</v>
+      </c>
+      <c r="D45" t="s">
+        <v>334</v>
+      </c>
+      <c r="E45" t="s">
+        <v>496</v>
+      </c>
+      <c r="F45" t="s">
         <v>497</v>
       </c>
-      <c r="B45" t="s">
+      <c r="H45" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="C45" t="s">
-        <v>503</v>
-      </c>
-      <c r="D45" t="s">
-        <v>315</v>
-      </c>
-      <c r="E45" t="s">
-        <v>500</v>
-      </c>
-      <c r="F45" t="s">
-        <v>501</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B46" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C46" t="s">
-        <v>505</v>
+        <v>377</v>
       </c>
       <c r="D46" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E46" t="s">
-        <v>500</v>
+        <v>372</v>
       </c>
       <c r="F46" t="s">
         <v>501</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B47" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="C47" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E47" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="F47" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="B48" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="C48" t="s">
-        <v>425</v>
+        <v>511</v>
       </c>
       <c r="D48" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E48" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="F48" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="B49" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="C49" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="D49" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E49" t="s">
-        <v>500</v>
+        <v>517</v>
       </c>
       <c r="F49" t="s">
-        <v>501</v>
+        <v>518</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>497</v>
+        <v>520</v>
       </c>
       <c r="B50" t="s">
-        <v>498</v>
+        <v>521</v>
       </c>
       <c r="C50" t="s">
-        <v>511</v>
+        <v>328</v>
       </c>
       <c r="D50" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E50" t="s">
-        <v>500</v>
+        <v>522</v>
       </c>
       <c r="F50" t="s">
-        <v>501</v>
+        <v>523</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>497</v>
+        <v>525</v>
       </c>
       <c r="B51" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="C51" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="D51" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E51" t="s">
-        <v>500</v>
+        <v>527</v>
       </c>
       <c r="F51" t="s">
-        <v>501</v>
+        <v>528</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>513</v>
+        <v>529</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>497</v>
+        <v>530</v>
       </c>
       <c r="B52" t="s">
-        <v>498</v>
+        <v>531</v>
       </c>
       <c r="C52" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E52" t="s">
-        <v>500</v>
+        <v>533</v>
       </c>
       <c r="F52" t="s">
-        <v>501</v>
+        <v>534</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>497</v>
+        <v>536</v>
       </c>
       <c r="B53" t="s">
-        <v>498</v>
+        <v>537</v>
       </c>
       <c r="C53" t="s">
-        <v>516</v>
+        <v>538</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E53" t="s">
-        <v>500</v>
+        <v>355</v>
       </c>
       <c r="F53" t="s">
-        <v>501</v>
+        <v>539</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>517</v>
+        <v>540</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="B54" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="C54" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E54" t="s">
-        <v>449</v>
+        <v>355</v>
       </c>
       <c r="F54" t="s">
-        <v>520</v>
+        <v>539</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>88</v>
+        <v>542</v>
       </c>
       <c r="B55" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="C55" t="s">
-        <v>309</v>
+        <v>544</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E55" t="s">
-        <v>523</v>
+        <v>545</v>
       </c>
       <c r="F55" t="s">
-        <v>524</v>
+        <v>546</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>525</v>
+        <v>547</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>526</v>
+        <v>548</v>
       </c>
       <c r="B56" t="s">
-        <v>527</v>
+        <v>549</v>
       </c>
       <c r="C56" t="s">
-        <v>528</v>
+        <v>316</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E56" t="s">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="F56" t="s">
-        <v>530</v>
+        <v>285</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>531</v>
+        <v>551</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="B57" t="s">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="C57" t="s">
-        <v>303</v>
+        <v>554</v>
       </c>
       <c r="D57" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E57" t="s">
-        <v>534</v>
+        <v>555</v>
       </c>
       <c r="F57" t="s">
-        <v>535</v>
+        <v>556</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>536</v>
+        <v>557</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="B58" t="s">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="C58" t="s">
-        <v>303</v>
+        <v>559</v>
       </c>
       <c r="D58" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E58" t="s">
-        <v>449</v>
+        <v>560</v>
       </c>
       <c r="F58" t="s">
-        <v>539</v>
+        <v>561</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>540</v>
+        <v>562</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>541</v>
+        <v>563</v>
       </c>
       <c r="B59" t="s">
-        <v>542</v>
+        <v>365</v>
       </c>
       <c r="C59" t="s">
-        <v>303</v>
+        <v>564</v>
       </c>
       <c r="D59" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E59" t="s">
-        <v>543</v>
+        <v>565</v>
       </c>
       <c r="F59" t="s">
-        <v>544</v>
+        <v>368</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>546</v>
+        <v>567</v>
       </c>
       <c r="B60" t="s">
-        <v>547</v>
+        <v>568</v>
       </c>
       <c r="C60" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="D60" t="s">
-        <v>315</v>
+        <v>284</v>
       </c>
       <c r="E60" t="s">
-        <v>548</v>
+        <v>285</v>
       </c>
       <c r="F60" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>550</v>
+        <v>570</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>551</v>
+        <v>571</v>
       </c>
       <c r="B61" t="s">
-        <v>552</v>
+        <v>572</v>
       </c>
       <c r="C61" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="D61" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E61" t="s">
-        <v>553</v>
+        <v>573</v>
       </c>
       <c r="F61" t="s">
-        <v>421</v>
+        <v>285</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>554</v>
+        <v>574</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>555</v>
+        <v>575</v>
       </c>
       <c r="B62" t="s">
-        <v>556</v>
+        <v>576</v>
       </c>
       <c r="C62" t="s">
-        <v>557</v>
+        <v>398</v>
       </c>
       <c r="D62" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E62" t="s">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="F62" t="s">
-        <v>559</v>
+        <v>578</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>560</v>
+        <v>579</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="B63" t="s">
-        <v>562</v>
+        <v>581</v>
       </c>
       <c r="C63" t="s">
-        <v>207</v>
+        <v>582</v>
       </c>
       <c r="D63" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E63" t="s">
-        <v>563</v>
+        <v>583</v>
       </c>
       <c r="F63" t="s">
-        <v>564</v>
+        <v>584</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>565</v>
+        <v>585</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>566</v>
+        <v>586</v>
       </c>
       <c r="B64" t="s">
-        <v>567</v>
+        <v>587</v>
       </c>
       <c r="C64" t="s">
-        <v>568</v>
+        <v>544</v>
       </c>
       <c r="D64" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E64" t="s">
-        <v>569</v>
+        <v>588</v>
       </c>
       <c r="F64" t="s">
-        <v>570</v>
+        <v>426</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>571</v>
+        <v>589</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>572</v>
+        <v>590</v>
       </c>
       <c r="B65" t="s">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="C65" t="s">
-        <v>297</v>
+        <v>592</v>
       </c>
       <c r="D65" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E65" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="F65" t="s">
-        <v>421</v>
+        <v>594</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>575</v>
+        <v>595</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>576</v>
+        <v>590</v>
       </c>
       <c r="B66" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="C66" t="s">
-        <v>503</v>
+        <v>596</v>
       </c>
       <c r="D66" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E66" t="s">
-        <v>578</v>
+        <v>593</v>
       </c>
       <c r="F66" t="s">
-        <v>293</v>
+        <v>594</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>579</v>
+        <v>597</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="B67" t="s">
-        <v>413</v>
+        <v>591</v>
       </c>
       <c r="C67" t="s">
-        <v>290</v>
+        <v>598</v>
       </c>
       <c r="D67" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E67" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="F67" t="s">
-        <v>415</v>
+        <v>594</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>582</v>
+        <v>599</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="B68" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="C68" t="s">
-        <v>309</v>
+        <v>398</v>
       </c>
       <c r="D68" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E68" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="F68" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>587</v>
+        <v>600</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B69" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C69" t="s">
-        <v>309</v>
+        <v>377</v>
       </c>
       <c r="D69" t="s">
-        <v>284</v>
+        <v>334</v>
       </c>
       <c r="E69" t="s">
-        <v>285</v>
+        <v>593</v>
       </c>
       <c r="F69" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B70" t="s">
+        <v>591</v>
+      </c>
+      <c r="C70" t="s">
+        <v>602</v>
+      </c>
+      <c r="D70" t="s">
+        <v>334</v>
+      </c>
+      <c r="E70" t="s">
         <v>593</v>
       </c>
-      <c r="C70" t="s">
-        <v>303</v>
-      </c>
-      <c r="D70" t="s">
-        <v>291</v>
-      </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>594</v>
       </c>
-      <c r="F70" t="s">
-        <v>286</v>
-      </c>
       <c r="H70" s="2" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="B71" t="s">
-        <v>463</v>
+        <v>591</v>
       </c>
       <c r="C71" t="s">
-        <v>303</v>
+        <v>604</v>
       </c>
       <c r="D71" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E71" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="F71" t="s">
-        <v>465</v>
+        <v>594</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="B72" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="C72" t="s">
-        <v>601</v>
+        <v>310</v>
       </c>
       <c r="D72" t="s">
-        <v>291</v>
+        <v>334</v>
       </c>
       <c r="E72" t="s">
-        <v>310</v>
+        <v>593</v>
       </c>
       <c r="F72" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="B73" t="s">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="C73" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D73" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E73" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="F73" t="s">
+        <v>594</v>
+      </c>
+      <c r="H73" s="2" t="s">
         <v>608</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>590</v>
+      </c>
+      <c r="B74" t="s">
+        <v>591</v>
+      </c>
+      <c r="C74" t="s">
+        <v>609</v>
+      </c>
+      <c r="D74" t="s">
+        <v>334</v>
+      </c>
+      <c r="E74" t="s">
+        <v>593</v>
+      </c>
+      <c r="F74" t="s">
+        <v>594</v>
+      </c>
+      <c r="H74" s="2" t="s">
         <v>610</v>
-      </c>
-      <c r="B74" t="s">
-        <v>605</v>
-      </c>
-      <c r="C74" t="s">
-        <v>303</v>
-      </c>
-      <c r="D74" t="s">
-        <v>291</v>
-      </c>
-      <c r="E74" t="s">
-        <v>611</v>
-      </c>
-      <c r="F74" t="s">
-        <v>524</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>611</v>
+      </c>
+      <c r="B75" t="s">
+        <v>420</v>
+      </c>
+      <c r="C75" t="s">
+        <v>612</v>
+      </c>
+      <c r="D75" t="s">
+        <v>334</v>
+      </c>
+      <c r="E75" t="s">
         <v>613</v>
       </c>
-      <c r="B75" t="s">
-        <v>346</v>
-      </c>
-      <c r="C75" t="s">
+      <c r="F75" t="s">
+        <v>426</v>
+      </c>
+      <c r="H75" s="2" t="s">
         <v>614</v>
-      </c>
-      <c r="D75" t="s">
-        <v>315</v>
-      </c>
-      <c r="E75" t="s">
-        <v>615</v>
-      </c>
-      <c r="F75" t="s">
-        <v>349</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>615</v>
+      </c>
+      <c r="B76" t="s">
+        <v>616</v>
+      </c>
+      <c r="C76" t="s">
+        <v>310</v>
+      </c>
+      <c r="D76" t="s">
+        <v>334</v>
+      </c>
+      <c r="E76" t="s">
+        <v>506</v>
+      </c>
+      <c r="F76" t="s">
         <v>617</v>
       </c>
-      <c r="B76" t="s">
-        <v>346</v>
-      </c>
-      <c r="C76" t="s">
+      <c r="H76" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="D76" t="s">
-        <v>315</v>
-      </c>
-      <c r="E76" t="s">
-        <v>619</v>
-      </c>
-      <c r="F76" t="s">
-        <v>349</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>88</v>
+      </c>
+      <c r="B77" t="s">
+        <v>619</v>
+      </c>
+      <c r="C77" t="s">
+        <v>328</v>
+      </c>
+      <c r="D77" t="s">
+        <v>334</v>
+      </c>
+      <c r="E77" t="s">
+        <v>620</v>
+      </c>
+      <c r="F77" t="s">
+        <v>534</v>
+      </c>
+      <c r="H77" s="2" t="s">
         <v>621</v>
-      </c>
-      <c r="B77" t="s">
-        <v>346</v>
-      </c>
-      <c r="C77" t="s">
-        <v>622</v>
-      </c>
-      <c r="D77" t="s">
-        <v>315</v>
-      </c>
-      <c r="E77" t="s">
-        <v>619</v>
-      </c>
-      <c r="F77" t="s">
-        <v>349</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>622</v>
+      </c>
+      <c r="B78" t="s">
+        <v>623</v>
+      </c>
+      <c r="C78" t="s">
         <v>624</v>
       </c>
-      <c r="B78" t="s">
+      <c r="D78" t="s">
+        <v>334</v>
+      </c>
+      <c r="E78" t="s">
         <v>625</v>
       </c>
-      <c r="C78" t="s">
-        <v>303</v>
-      </c>
-      <c r="D78" t="s">
-        <v>291</v>
-      </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
+        <v>324</v>
+      </c>
+      <c r="H78" s="2" t="s">
         <v>626</v>
-      </c>
-      <c r="F78" t="s">
-        <v>627</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>627</v>
+      </c>
+      <c r="B79" t="s">
+        <v>628</v>
+      </c>
+      <c r="C79" t="s">
+        <v>316</v>
+      </c>
+      <c r="D79" t="s">
+        <v>334</v>
+      </c>
+      <c r="E79" t="s">
         <v>629</v>
       </c>
-      <c r="B79" t="s">
+      <c r="F79" t="s">
         <v>630</v>
       </c>
-      <c r="C79" t="s">
-        <v>309</v>
-      </c>
-      <c r="D79" t="s">
-        <v>315</v>
-      </c>
-      <c r="E79" t="s">
+      <c r="H79" s="2" t="s">
         <v>631</v>
-      </c>
-      <c r="F79" t="s">
-        <v>632</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>632</v>
+      </c>
+      <c r="B80" t="s">
+        <v>633</v>
+      </c>
+      <c r="C80" t="s">
+        <v>316</v>
+      </c>
+      <c r="D80" t="s">
+        <v>334</v>
+      </c>
+      <c r="E80" t="s">
+        <v>506</v>
+      </c>
+      <c r="F80" t="s">
         <v>634</v>
       </c>
-      <c r="B80" t="s">
+      <c r="H80" s="2" t="s">
         <v>635</v>
-      </c>
-      <c r="C80" t="s">
-        <v>636</v>
-      </c>
-      <c r="D80" t="s">
-        <v>315</v>
-      </c>
-      <c r="E80" t="s">
-        <v>637</v>
-      </c>
-      <c r="F80" t="s">
-        <v>638</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B81" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="C81" t="s">
-        <v>642</v>
+        <v>316</v>
       </c>
       <c r="D81" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E81" t="s">
-        <v>643</v>
+        <v>512</v>
       </c>
       <c r="F81" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="B82" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C82" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="D82" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E82" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="F82" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="B83" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C83" t="s">
-        <v>653</v>
+        <v>316</v>
       </c>
       <c r="D83" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E83" t="s">
-        <v>285</v>
+        <v>647</v>
       </c>
       <c r="F83" t="s">
-        <v>654</v>
+        <v>462</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="B84" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="C84" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="D84" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E84" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="F84" t="s">
-        <v>421</v>
+        <v>652</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="B85" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="C85" t="s">
-        <v>303</v>
+        <v>544</v>
       </c>
       <c r="D85" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E85" t="s">
-        <v>662</v>
+        <v>285</v>
       </c>
       <c r="F85" t="s">
-        <v>663</v>
+        <v>285</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="B86" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="C86" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="D86" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E86" t="s">
-        <v>449</v>
+        <v>660</v>
       </c>
       <c r="F86" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="B87" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="C87" t="s">
-        <v>303</v>
+        <v>544</v>
       </c>
       <c r="D87" t="s">
-        <v>291</v>
+        <v>334</v>
       </c>
       <c r="E87" t="s">
-        <v>671</v>
+        <v>422</v>
       </c>
       <c r="F87" t="s">
-        <v>530</v>
+        <v>664</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="B88" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="C88" t="s">
-        <v>309</v>
+        <v>207</v>
       </c>
       <c r="D88" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E88" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="F88" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="B89" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="C89" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="D89" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E89" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="F89" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="B90" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="C90" t="s">
-        <v>686</v>
+        <v>310</v>
       </c>
       <c r="D90" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E90" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="F90" t="s">
-        <v>349</v>
+        <v>462</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>681</v>
+      </c>
+      <c r="B91" t="s">
+        <v>682</v>
+      </c>
+      <c r="C91" t="s">
+        <v>596</v>
+      </c>
+      <c r="D91" t="s">
+        <v>334</v>
+      </c>
+      <c r="E91" t="s">
+        <v>683</v>
+      </c>
+      <c r="F91" t="s">
+        <v>306</v>
+      </c>
+      <c r="H91" s="2" t="s">
         <v>684</v>
-      </c>
-      <c r="B91" t="s">
-        <v>552</v>
-      </c>
-      <c r="C91" t="s">
-        <v>303</v>
-      </c>
-      <c r="D91" t="s">
-        <v>315</v>
-      </c>
-      <c r="E91" t="s">
-        <v>689</v>
-      </c>
-      <c r="F91" t="s">
-        <v>421</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="B92" t="s">
-        <v>346</v>
+        <v>449</v>
       </c>
       <c r="C92" t="s">
-        <v>692</v>
+        <v>303</v>
       </c>
       <c r="D92" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E92" t="s">
-        <v>619</v>
+        <v>686</v>
       </c>
       <c r="F92" t="s">
-        <v>349</v>
+        <v>451</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="B93" t="s">
-        <v>552</v>
+        <v>689</v>
       </c>
       <c r="C93" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="D93" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E93" t="s">
-        <v>695</v>
+        <v>588</v>
       </c>
       <c r="F93" t="s">
-        <v>421</v>
+        <v>690</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="B94" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="C94" t="s">
-        <v>493</v>
+        <v>692</v>
       </c>
       <c r="D94" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E94" t="s">
-        <v>699</v>
+        <v>588</v>
       </c>
       <c r="F94" t="s">
-        <v>285</v>
+        <v>690</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="B95" t="s">
-        <v>702</v>
+        <v>689</v>
       </c>
       <c r="C95" t="s">
-        <v>303</v>
+        <v>455</v>
       </c>
       <c r="D95" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E95" t="s">
-        <v>703</v>
+        <v>588</v>
       </c>
       <c r="F95" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="B96" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="C96" t="s">
-        <v>708</v>
+        <v>328</v>
       </c>
       <c r="D96" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E96" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="F96" t="s">
-        <v>710</v>
+        <v>698</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>711</v>
+        <v>699</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="B97" t="s">
-        <v>335</v>
+        <v>701</v>
       </c>
       <c r="C97" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="D97" t="s">
-        <v>315</v>
+        <v>284</v>
       </c>
       <c r="E97" t="s">
-        <v>713</v>
+        <v>285</v>
       </c>
       <c r="F97" t="s">
-        <v>337</v>
+        <v>702</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="B98" t="s">
-        <v>335</v>
+        <v>705</v>
       </c>
       <c r="C98" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="D98" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="E98" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="F98" t="s">
-        <v>337</v>
+        <v>286</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
       <c r="B99" t="s">
-        <v>718</v>
+        <v>537</v>
       </c>
       <c r="C99" t="s">
-        <v>719</v>
+        <v>316</v>
       </c>
       <c r="D99" t="s">
-        <v>398</v>
+        <v>334</v>
       </c>
       <c r="E99" t="s">
-        <v>285</v>
+        <v>709</v>
       </c>
       <c r="F99" t="s">
-        <v>720</v>
+        <v>539</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="B100" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="C100" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="D100" t="s">
-        <v>398</v>
+        <v>304</v>
       </c>
       <c r="E100" t="s">
-        <v>285</v>
+        <v>329</v>
       </c>
       <c r="F100" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="B101" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="C101" t="s">
-        <v>309</v>
+        <v>718</v>
       </c>
       <c r="D101" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E101" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="F101" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>722</v>
+      </c>
+      <c r="B102" t="s">
+        <v>717</v>
+      </c>
+      <c r="C102" t="s">
+        <v>316</v>
+      </c>
+      <c r="D102" t="s">
+        <v>304</v>
+      </c>
+      <c r="E102" t="s">
+        <v>723</v>
+      </c>
+      <c r="F102" t="s">
+        <v>534</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>725</v>
+      </c>
+      <c r="B103" t="s">
+        <v>365</v>
+      </c>
+      <c r="C103" t="s">
+        <v>726</v>
+      </c>
+      <c r="D103" t="s">
+        <v>334</v>
+      </c>
+      <c r="E103" t="s">
+        <v>727</v>
+      </c>
+      <c r="F103" t="s">
+        <v>368</v>
+      </c>
+      <c r="H103" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="B102" t="s">
-        <v>413</v>
-      </c>
-      <c r="C102" t="s">
-        <v>290</v>
-      </c>
-      <c r="D102" t="s">
-        <v>315</v>
-      </c>
-      <c r="E102" t="s">
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>729</v>
       </c>
-      <c r="F102" t="s">
-        <v>415</v>
-      </c>
-      <c r="H102" s="2" t="s">
+      <c r="B104" t="s">
+        <v>365</v>
+      </c>
+      <c r="C104" t="s">
         <v>730</v>
+      </c>
+      <c r="D104" t="s">
+        <v>334</v>
+      </c>
+      <c r="E104" t="s">
+        <v>731</v>
+      </c>
+      <c r="F104" t="s">
+        <v>368</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>733</v>
+      </c>
+      <c r="B105" t="s">
+        <v>365</v>
+      </c>
+      <c r="C105" t="s">
+        <v>734</v>
+      </c>
+      <c r="D105" t="s">
+        <v>334</v>
+      </c>
+      <c r="E105" t="s">
+        <v>731</v>
+      </c>
+      <c r="F105" t="s">
+        <v>368</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>736</v>
+      </c>
+      <c r="B106" t="s">
+        <v>650</v>
+      </c>
+      <c r="C106" t="s">
+        <v>328</v>
+      </c>
+      <c r="D106" t="s">
+        <v>334</v>
+      </c>
+      <c r="E106" t="s">
+        <v>737</v>
+      </c>
+      <c r="F106" t="s">
+        <v>652</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>739</v>
+      </c>
+      <c r="B107" t="s">
+        <v>740</v>
+      </c>
+      <c r="C107" t="s">
+        <v>316</v>
+      </c>
+      <c r="D107" t="s">
+        <v>304</v>
+      </c>
+      <c r="E107" t="s">
+        <v>741</v>
+      </c>
+      <c r="F107" t="s">
+        <v>742</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>744</v>
+      </c>
+      <c r="B108" t="s">
+        <v>745</v>
+      </c>
+      <c r="C108" t="s">
+        <v>328</v>
+      </c>
+      <c r="D108" t="s">
+        <v>334</v>
+      </c>
+      <c r="E108" t="s">
+        <v>746</v>
+      </c>
+      <c r="F108" t="s">
+        <v>747</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>749</v>
+      </c>
+      <c r="B109" t="s">
+        <v>750</v>
+      </c>
+      <c r="C109" t="s">
+        <v>455</v>
+      </c>
+      <c r="D109" t="s">
+        <v>334</v>
+      </c>
+      <c r="E109" t="s">
+        <v>751</v>
+      </c>
+      <c r="F109" t="s">
+        <v>752</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>754</v>
+      </c>
+      <c r="B110" t="s">
+        <v>755</v>
+      </c>
+      <c r="C110" t="s">
+        <v>756</v>
+      </c>
+      <c r="D110" t="s">
+        <v>334</v>
+      </c>
+      <c r="E110" t="s">
+        <v>757</v>
+      </c>
+      <c r="F110" t="s">
+        <v>758</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>760</v>
+      </c>
+      <c r="B111" t="s">
+        <v>761</v>
+      </c>
+      <c r="C111" t="s">
+        <v>328</v>
+      </c>
+      <c r="D111" t="s">
+        <v>334</v>
+      </c>
+      <c r="E111" t="s">
+        <v>285</v>
+      </c>
+      <c r="F111" t="s">
+        <v>285</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>763</v>
+      </c>
+      <c r="B112" t="s">
+        <v>764</v>
+      </c>
+      <c r="C112" t="s">
+        <v>316</v>
+      </c>
+      <c r="D112" t="s">
+        <v>334</v>
+      </c>
+      <c r="E112" t="s">
+        <v>765</v>
+      </c>
+      <c r="F112" t="s">
+        <v>766</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>768</v>
+      </c>
+      <c r="B113" t="s">
+        <v>769</v>
+      </c>
+      <c r="C113" t="s">
+        <v>770</v>
+      </c>
+      <c r="D113" t="s">
+        <v>334</v>
+      </c>
+      <c r="E113" t="s">
+        <v>285</v>
+      </c>
+      <c r="F113" t="s">
+        <v>771</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>773</v>
+      </c>
+      <c r="B114" t="s">
+        <v>774</v>
+      </c>
+      <c r="C114" t="s">
+        <v>316</v>
+      </c>
+      <c r="D114" t="s">
+        <v>334</v>
+      </c>
+      <c r="E114" t="s">
+        <v>775</v>
+      </c>
+      <c r="F114" t="s">
+        <v>462</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>777</v>
+      </c>
+      <c r="B115" t="s">
+        <v>778</v>
+      </c>
+      <c r="C115" t="s">
+        <v>316</v>
+      </c>
+      <c r="D115" t="s">
+        <v>334</v>
+      </c>
+      <c r="E115" t="s">
+        <v>779</v>
+      </c>
+      <c r="F115" t="s">
+        <v>780</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>782</v>
+      </c>
+      <c r="B116" t="s">
+        <v>783</v>
+      </c>
+      <c r="C116" t="s">
+        <v>784</v>
+      </c>
+      <c r="D116" t="s">
+        <v>334</v>
+      </c>
+      <c r="E116" t="s">
+        <v>506</v>
+      </c>
+      <c r="F116" t="s">
+        <v>785</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>787</v>
+      </c>
+      <c r="B117" t="s">
+        <v>717</v>
+      </c>
+      <c r="C117" t="s">
+        <v>316</v>
+      </c>
+      <c r="D117" t="s">
+        <v>304</v>
+      </c>
+      <c r="E117" t="s">
+        <v>788</v>
+      </c>
+      <c r="F117" t="s">
+        <v>324</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>790</v>
+      </c>
+      <c r="B118" t="s">
+        <v>791</v>
+      </c>
+      <c r="C118" t="s">
+        <v>328</v>
+      </c>
+      <c r="D118" t="s">
+        <v>334</v>
+      </c>
+      <c r="E118" t="s">
+        <v>792</v>
+      </c>
+      <c r="F118" t="s">
+        <v>793</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>795</v>
+      </c>
+      <c r="B119" t="s">
+        <v>796</v>
+      </c>
+      <c r="C119" t="s">
+        <v>328</v>
+      </c>
+      <c r="D119" t="s">
+        <v>334</v>
+      </c>
+      <c r="E119" t="s">
+        <v>797</v>
+      </c>
+      <c r="F119" t="s">
+        <v>798</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>800</v>
+      </c>
+      <c r="B120" t="s">
+        <v>801</v>
+      </c>
+      <c r="C120" t="s">
+        <v>303</v>
+      </c>
+      <c r="D120" t="s">
+        <v>334</v>
+      </c>
+      <c r="E120" t="s">
+        <v>802</v>
+      </c>
+      <c r="F120" t="s">
+        <v>803</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>805</v>
+      </c>
+      <c r="B121" t="s">
+        <v>806</v>
+      </c>
+      <c r="C121" t="s">
+        <v>455</v>
+      </c>
+      <c r="D121" t="s">
+        <v>334</v>
+      </c>
+      <c r="E121" t="s">
+        <v>807</v>
+      </c>
+      <c r="F121" t="s">
+        <v>808</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>810</v>
+      </c>
+      <c r="B122" t="s">
+        <v>482</v>
+      </c>
+      <c r="C122" t="s">
+        <v>303</v>
+      </c>
+      <c r="D122" t="s">
+        <v>334</v>
+      </c>
+      <c r="E122" t="s">
+        <v>483</v>
+      </c>
+      <c r="F122" t="s">
+        <v>811</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>813</v>
+      </c>
+      <c r="B123" t="s">
+        <v>814</v>
+      </c>
+      <c r="C123" t="s">
+        <v>609</v>
+      </c>
+      <c r="D123" t="s">
+        <v>334</v>
+      </c>
+      <c r="E123" t="s">
+        <v>815</v>
+      </c>
+      <c r="F123" t="s">
+        <v>292</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>817</v>
+      </c>
+      <c r="B124" t="s">
+        <v>818</v>
+      </c>
+      <c r="C124" t="s">
+        <v>819</v>
+      </c>
+      <c r="D124" t="s">
+        <v>334</v>
+      </c>
+      <c r="E124" t="s">
+        <v>820</v>
+      </c>
+      <c r="F124" t="s">
+        <v>821</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>823</v>
+      </c>
+      <c r="B125" t="s">
+        <v>824</v>
+      </c>
+      <c r="C125" t="s">
+        <v>825</v>
+      </c>
+      <c r="D125" t="s">
+        <v>334</v>
+      </c>
+      <c r="E125" t="s">
+        <v>826</v>
+      </c>
+      <c r="F125" t="s">
+        <v>368</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>823</v>
+      </c>
+      <c r="B126" t="s">
+        <v>646</v>
+      </c>
+      <c r="C126" t="s">
+        <v>316</v>
+      </c>
+      <c r="D126" t="s">
+        <v>334</v>
+      </c>
+      <c r="E126" t="s">
+        <v>828</v>
+      </c>
+      <c r="F126" t="s">
+        <v>462</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>830</v>
+      </c>
+      <c r="B127" t="s">
+        <v>365</v>
+      </c>
+      <c r="C127" t="s">
+        <v>831</v>
+      </c>
+      <c r="D127" t="s">
+        <v>334</v>
+      </c>
+      <c r="E127" t="s">
+        <v>731</v>
+      </c>
+      <c r="F127" t="s">
+        <v>368</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>833</v>
+      </c>
+      <c r="B128" t="s">
+        <v>834</v>
+      </c>
+      <c r="C128" t="s">
+        <v>835</v>
+      </c>
+      <c r="D128" t="s">
+        <v>334</v>
+      </c>
+      <c r="E128" t="s">
+        <v>836</v>
+      </c>
+      <c r="F128" t="s">
+        <v>837</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>839</v>
+      </c>
+      <c r="B129" t="s">
+        <v>646</v>
+      </c>
+      <c r="C129" t="s">
+        <v>316</v>
+      </c>
+      <c r="D129" t="s">
+        <v>334</v>
+      </c>
+      <c r="E129" t="s">
+        <v>840</v>
+      </c>
+      <c r="F129" t="s">
+        <v>462</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>842</v>
+      </c>
+      <c r="B130" t="s">
+        <v>843</v>
+      </c>
+      <c r="C130" t="s">
+        <v>328</v>
+      </c>
+      <c r="D130" t="s">
+        <v>334</v>
+      </c>
+      <c r="E130" t="s">
+        <v>844</v>
+      </c>
+      <c r="F130" t="s">
+        <v>845</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>847</v>
+      </c>
+      <c r="B131" t="s">
+        <v>843</v>
+      </c>
+      <c r="C131" t="s">
+        <v>848</v>
+      </c>
+      <c r="D131" t="s">
+        <v>334</v>
+      </c>
+      <c r="E131" t="s">
+        <v>849</v>
+      </c>
+      <c r="F131" t="s">
+        <v>845</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>851</v>
+      </c>
+      <c r="B132" t="s">
+        <v>852</v>
+      </c>
+      <c r="C132" t="s">
+        <v>398</v>
+      </c>
+      <c r="D132" t="s">
+        <v>334</v>
+      </c>
+      <c r="E132" t="s">
+        <v>853</v>
+      </c>
+      <c r="F132" t="s">
+        <v>285</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>855</v>
+      </c>
+      <c r="B133" t="s">
+        <v>397</v>
+      </c>
+      <c r="C133" t="s">
+        <v>59</v>
+      </c>
+      <c r="D133" t="s">
+        <v>295</v>
+      </c>
+      <c r="E133" t="s">
+        <v>856</v>
+      </c>
+      <c r="F133" t="s">
+        <v>285</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>858</v>
+      </c>
+      <c r="B134" t="s">
+        <v>801</v>
+      </c>
+      <c r="C134" t="s">
+        <v>848</v>
+      </c>
+      <c r="D134" t="s">
+        <v>295</v>
+      </c>
+      <c r="E134" t="s">
+        <v>859</v>
+      </c>
+      <c r="F134" t="s">
+        <v>803</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>861</v>
+      </c>
+      <c r="B135" t="s">
+        <v>862</v>
+      </c>
+      <c r="C135" t="s">
+        <v>316</v>
+      </c>
+      <c r="D135" t="s">
+        <v>334</v>
+      </c>
+      <c r="E135" t="s">
+        <v>863</v>
+      </c>
+      <c r="F135" t="s">
+        <v>864</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>866</v>
+      </c>
+      <c r="B136" t="s">
+        <v>867</v>
+      </c>
+      <c r="C136" t="s">
+        <v>421</v>
+      </c>
+      <c r="D136" t="s">
+        <v>334</v>
+      </c>
+      <c r="E136" t="s">
+        <v>868</v>
+      </c>
+      <c r="F136" t="s">
+        <v>869</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>871</v>
+      </c>
+      <c r="B137" t="s">
+        <v>354</v>
+      </c>
+      <c r="C137" t="s">
+        <v>316</v>
+      </c>
+      <c r="D137" t="s">
+        <v>334</v>
+      </c>
+      <c r="E137" t="s">
+        <v>872</v>
+      </c>
+      <c r="F137" t="s">
+        <v>356</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>874</v>
+      </c>
+      <c r="B138" t="s">
+        <v>354</v>
+      </c>
+      <c r="C138" t="s">
+        <v>316</v>
+      </c>
+      <c r="D138" t="s">
+        <v>334</v>
+      </c>
+      <c r="E138" t="s">
+        <v>872</v>
+      </c>
+      <c r="F138" t="s">
+        <v>356</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>876</v>
+      </c>
+      <c r="B139" t="s">
+        <v>877</v>
+      </c>
+      <c r="C139" t="s">
+        <v>878</v>
+      </c>
+      <c r="D139" t="s">
+        <v>295</v>
+      </c>
+      <c r="E139" t="s">
+        <v>285</v>
+      </c>
+      <c r="F139" t="s">
+        <v>879</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>876</v>
+      </c>
+      <c r="B140" t="s">
+        <v>877</v>
+      </c>
+      <c r="C140" t="s">
+        <v>878</v>
+      </c>
+      <c r="D140" t="s">
+        <v>295</v>
+      </c>
+      <c r="E140" t="s">
+        <v>285</v>
+      </c>
+      <c r="F140" t="s">
+        <v>879</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>882</v>
+      </c>
+      <c r="B141" t="s">
+        <v>883</v>
+      </c>
+      <c r="C141" t="s">
+        <v>328</v>
+      </c>
+      <c r="D141" t="s">
+        <v>334</v>
+      </c>
+      <c r="E141" t="s">
+        <v>884</v>
+      </c>
+      <c r="F141" t="s">
+        <v>885</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>887</v>
+      </c>
+      <c r="B142" t="s">
+        <v>449</v>
+      </c>
+      <c r="C142" t="s">
+        <v>303</v>
+      </c>
+      <c r="D142" t="s">
+        <v>334</v>
+      </c>
+      <c r="E142" t="s">
+        <v>888</v>
+      </c>
+      <c r="F142" t="s">
+        <v>451</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>889</v>
       </c>
     </row>
   </sheetData>
@@ -6524,6 +7921,46 @@
     <hyperlink ref="H100" r:id="rId99"/>
     <hyperlink ref="H101" r:id="rId100"/>
     <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
